--- a/StockInfo/tse_analysis_result.xlsx
+++ b/StockInfo/tse_analysis_result.xlsx
@@ -28076,16 +28076,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>24.51</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>95037</v>
       </c>
@@ -28109,16 +28101,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>23.67</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+0.24</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>84602</v>
       </c>
@@ -28142,16 +28126,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>10.34</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+0.04</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>76487</v>
       </c>
@@ -28175,16 +28151,8 @@
           <t xml:space="preserve">聯電            </t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>76.90</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+3.9</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>52636</v>
       </c>
@@ -28208,16 +28176,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+0.42</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>47209</v>
       </c>
@@ -28241,16 +28201,8 @@
           <t xml:space="preserve">華邦電          </t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>85.70</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>42842</v>
       </c>
@@ -28274,16 +28226,8 @@
           <t xml:space="preserve">臺企銀          </t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>16.90</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>38511</v>
       </c>
@@ -28307,16 +28251,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>23.54</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+0.13</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>34633</v>
       </c>
@@ -28340,16 +28276,8 @@
           <t xml:space="preserve">緯創            </t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>140.50</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>33082</v>
       </c>
@@ -28373,16 +28301,8 @@
           <t xml:space="preserve">力積電          </t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>51.40</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>30405</v>
       </c>
@@ -28406,16 +28326,8 @@
           <t xml:space="preserve">群創            </t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>22782</v>
       </c>
@@ -28439,16 +28351,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>9.03</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>22452</v>
       </c>
@@ -28472,16 +28376,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>X0.0</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>21895</v>
       </c>
@@ -28505,16 +28401,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>54.20</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>13840</v>
       </c>
@@ -28538,16 +28426,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+0.36</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>11527</v>
       </c>
@@ -28571,16 +28451,8 @@
           <t>統一台灣高息動能</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>16.70</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>10980</v>
       </c>
@@ -28604,16 +28476,8 @@
           <t xml:space="preserve">英業達          </t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>46.60</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>10561</v>
       </c>
@@ -28637,16 +28501,8 @@
           <t xml:space="preserve">鴻海            </t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>207.50</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>10408</v>
       </c>
@@ -28670,16 +28526,8 @@
           <t xml:space="preserve">南亞科          </t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>207.00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>8651</v>
       </c>
@@ -28703,16 +28551,8 @@
           <t xml:space="preserve">廣達            </t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>329.00</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>7042</v>
       </c>
@@ -28736,16 +28576,8 @@
           <t xml:space="preserve">光寶科          </t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>165.00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>6523</v>
       </c>
@@ -28769,16 +28601,8 @@
           <t xml:space="preserve">聯合再生        </t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>17.20</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>6519</v>
       </c>
@@ -28802,16 +28626,8 @@
           <t xml:space="preserve">盟立            </t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>86.90</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+7.9</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>6080</v>
       </c>
@@ -28835,16 +28651,8 @@
           <t xml:space="preserve">三商壽          </t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>7.88</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+0.01</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>5651</v>
       </c>
@@ -28868,16 +28676,8 @@
           <t xml:space="preserve">玉山金          </t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>32.85</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>5546</v>
       </c>
@@ -28901,16 +28701,8 @@
           <t xml:space="preserve">元大金          </t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>51.20</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>5365</v>
       </c>
@@ -28934,16 +28726,8 @@
           <t xml:space="preserve">燿華            </t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>65.60</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>-2.9</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>4843</v>
       </c>
@@ -28967,16 +28751,8 @@
           <t xml:space="preserve">台聚            </t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>4786</v>
       </c>
@@ -29000,16 +28776,8 @@
           <t xml:space="preserve">中租-KY         </t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>120.00</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>4730</v>
       </c>
@@ -29033,16 +28801,8 @@
           <t xml:space="preserve">景碩            </t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>430.50</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+39.0</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>4635</v>
       </c>
@@ -29066,16 +28826,8 @@
           <t xml:space="preserve">華新            </t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+1.35</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>4315</v>
       </c>
@@ -29099,16 +28851,8 @@
           <t xml:space="preserve">台亞            </t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>35.50</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+3.2</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>4252</v>
       </c>
@@ -29132,16 +28876,8 @@
           <t xml:space="preserve">中石化          </t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>7.75</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>4119</v>
       </c>
@@ -29165,11 +28901,7 @@
           <t xml:space="preserve">中信金          </t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>53.10</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>3728</v>
@@ -29194,16 +28926,8 @@
           <t xml:space="preserve">精成科          </t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>114.50</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>3697</v>
       </c>
@@ -29227,16 +28951,8 @@
           <t xml:space="preserve">矽統            </t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>55.60</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>3081</v>
       </c>
@@ -29260,16 +28976,8 @@
           <t xml:space="preserve">超豐            </t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>90.30</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>3002</v>
       </c>
@@ -29293,16 +29001,8 @@
           <t xml:space="preserve">統一證          </t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>2936</v>
       </c>
@@ -29326,16 +29026,8 @@
           <t xml:space="preserve">智原            </t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>174.50</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+15.5</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>2783</v>
       </c>
@@ -29359,16 +29051,8 @@
           <t xml:space="preserve">新日興          </t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>204.00</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>2664</v>
       </c>
@@ -29392,11 +29076,7 @@
           <t xml:space="preserve">彰銀            </t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>21.60</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>2585</v>
@@ -29421,16 +29101,8 @@
           <t xml:space="preserve">可寧衛*         </t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>29.70</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>2510</v>
       </c>
@@ -29454,16 +29126,8 @@
           <t xml:space="preserve">元晶            </t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>39.10</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>2495</v>
       </c>
@@ -29487,16 +29151,8 @@
           <t xml:space="preserve">華南金          </t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>35.90</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>2386</v>
       </c>
@@ -29520,16 +29176,8 @@
           <t xml:space="preserve">偉詮電          </t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>68.30</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+5.2</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>2342</v>
       </c>
@@ -29553,16 +29201,8 @@
           <t xml:space="preserve">中華電          </t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>137.00</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>2283</v>
       </c>
@@ -29586,16 +29226,8 @@
           <t xml:space="preserve">晶豪科          </t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>150.50</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>2281</v>
       </c>
@@ -29619,16 +29251,8 @@
           <t xml:space="preserve">華泰            </t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>62.20</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>2155</v>
       </c>
@@ -29652,16 +29276,8 @@
           <t xml:space="preserve">彩晶            </t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>9.09</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+0.14</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>2141</v>
       </c>
@@ -29685,16 +29301,8 @@
           <t xml:space="preserve">信錦            </t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>107.00</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+7.8</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>2139</v>
       </c>
@@ -29718,16 +29326,8 @@
           <t xml:space="preserve">台達化          </t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>19.10</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>2114</v>
       </c>
@@ -29751,16 +29351,8 @@
           <t xml:space="preserve">南茂            </t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>67.40</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>2092</v>
       </c>
@@ -29784,16 +29376,8 @@
           <t xml:space="preserve">台化            </t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>50.50</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>2078</v>
       </c>
@@ -29817,16 +29401,8 @@
           <t xml:space="preserve">志超            </t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+2.05</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>1982</v>
       </c>
@@ -29850,16 +29426,8 @@
           <t xml:space="preserve">雷虎            </t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>154.50</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>1930</v>
       </c>
@@ -29883,16 +29451,8 @@
           <t xml:space="preserve">菱生            </t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>30.25</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>1863</v>
       </c>
@@ -29916,16 +29476,8 @@
           <t xml:space="preserve">華新科          </t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>149.50</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>1857</v>
       </c>
@@ -29949,16 +29501,8 @@
           <t xml:space="preserve">矽力*-KY        </t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>365.50</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+33.0</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>1850</v>
       </c>
@@ -29982,16 +29526,8 @@
           <t xml:space="preserve">中信中國高股息  </t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>15.59</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>1763</v>
       </c>
@@ -30015,16 +29551,8 @@
           <t xml:space="preserve">瑞昱            </t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>538.00</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>1742</v>
       </c>
@@ -30048,16 +29576,8 @@
           <t xml:space="preserve">合勤控          </t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>38.00</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>1725</v>
       </c>
@@ -30081,16 +29601,8 @@
           <t xml:space="preserve">瀚荃            </t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>100.50</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+7.4</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>1601</v>
       </c>
@@ -30114,16 +29626,8 @@
           <t xml:space="preserve">王道銀行        </t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>10.30</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>1562</v>
       </c>
@@ -30147,16 +29651,8 @@
           <t xml:space="preserve">正達            </t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>46.50</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+4.2</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>1521</v>
       </c>
@@ -30180,16 +29676,8 @@
           <t xml:space="preserve">正崴            </t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>40.25</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+3.65</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>1463</v>
       </c>
@@ -30213,16 +29701,8 @@
           <t xml:space="preserve">永光            </t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>52.70</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+4.75</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>1429</v>
       </c>
@@ -30246,16 +29726,8 @@
           <t xml:space="preserve">普安            </t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>42.45</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>1394</v>
       </c>
@@ -30279,16 +29751,8 @@
           <t xml:space="preserve">映泰            </t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>38.15</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+2.9</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>1381</v>
       </c>
@@ -30312,16 +29776,8 @@
           <t xml:space="preserve">文曄            </t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>217.00</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>-13.0</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>1347</v>
       </c>
@@ -30345,16 +29801,8 @@
           <t xml:space="preserve">樺漢            </t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>310.00</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>1340</v>
       </c>
@@ -30378,16 +29826,8 @@
           <t xml:space="preserve">裕隆            </t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>27.70</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>1242</v>
       </c>
@@ -30411,16 +29851,8 @@
           <t xml:space="preserve">台新新光金      </t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>24.25</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>1226</v>
       </c>
@@ -30444,16 +29876,8 @@
           <t xml:space="preserve">東台            </t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>35.10</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>1211</v>
       </c>
@@ -30477,16 +29901,8 @@
           <t xml:space="preserve">希華            </t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>46.60</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+4.2</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>1197</v>
       </c>
@@ -30510,16 +29926,8 @@
           <t xml:space="preserve">遠東銀          </t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>12.60</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>1195</v>
       </c>
@@ -30543,16 +29951,8 @@
           <t xml:space="preserve">宏全            </t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>1191</v>
       </c>
@@ -30576,16 +29976,8 @@
           <t xml:space="preserve">玉晶光          </t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>544.00</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+41.0</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>1180</v>
       </c>
@@ -30609,16 +30001,8 @@
           <t xml:space="preserve">光聖            </t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>2,370.00</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>+215.0</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>1161</v>
       </c>
@@ -30642,16 +30026,8 @@
           <t xml:space="preserve">富邦台50        </t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>196.00</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+1.15</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>1145</v>
       </c>
@@ -30675,16 +30051,8 @@
           <t xml:space="preserve">嘉晶            </t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>65.90</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>1140</v>
       </c>
@@ -30708,16 +30076,8 @@
           <t xml:space="preserve">長華*           </t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>48.50</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>1080</v>
       </c>
@@ -30741,16 +30101,8 @@
           <t xml:space="preserve">艾笛森          </t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>27.20</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+2.45</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>1038</v>
       </c>
@@ -30774,16 +30126,8 @@
           <t xml:space="preserve">南電            </t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>796.00</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+72.0</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>1038</v>
       </c>
@@ -30807,16 +30151,8 @@
           <t xml:space="preserve">群益證          </t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>28.20</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>1034</v>
       </c>
@@ -30840,16 +30176,8 @@
           <t xml:space="preserve">台汽電          </t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>46.20</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>1009</v>
       </c>
@@ -30873,16 +30201,8 @@
           <t xml:space="preserve">統一FANG+       </t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>118.10</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>1006</v>
       </c>
@@ -30906,16 +30226,8 @@
           <t xml:space="preserve">精金            </t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>995</v>
       </c>
@@ -30939,16 +30251,8 @@
           <t>國泰台灣科技龍頭</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>42.96</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>975</v>
       </c>
@@ -30972,16 +30276,8 @@
           <t xml:space="preserve">長榮航太        </t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>166.00</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>964</v>
       </c>
@@ -31005,16 +30301,8 @@
           <t xml:space="preserve">友勁            </t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>964</v>
       </c>
@@ -31038,16 +30326,8 @@
           <t xml:space="preserve">亞聚            </t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>947</v>
       </c>
@@ -31071,16 +30351,8 @@
           <t xml:space="preserve">建漢            </t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>30.25</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>945</v>
       </c>
@@ -31104,16 +30376,8 @@
           <t xml:space="preserve">迅得            </t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>185.00</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>927</v>
       </c>
@@ -31137,11 +30401,7 @@
           <t xml:space="preserve">益登            </t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>39.35</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
       <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>924</v>
@@ -31166,16 +30426,8 @@
           <t xml:space="preserve">技嘉            </t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>279.00</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>912</v>
       </c>
@@ -31199,16 +30451,8 @@
           <t xml:space="preserve">華東            </t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>46.20</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>884</v>
       </c>
@@ -31232,16 +30476,8 @@
           <t xml:space="preserve">今國光          </t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>65.90</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+3.8</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>872</v>
       </c>
@@ -31265,11 +30501,7 @@
           <t xml:space="preserve">神達            </t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>84.10</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>869</v>
@@ -31294,16 +30526,8 @@
           <t xml:space="preserve">榮創            </t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>29.90</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+2.7</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>865</v>
       </c>
@@ -31327,16 +30551,8 @@
           <t xml:space="preserve">愛山林          </t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>56.90</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+2.9</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>841</v>
       </c>
@@ -31437,16 +30653,8 @@
           <t xml:space="preserve">台玻            </t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>70.90</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-3.3</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-63960</v>
       </c>
@@ -31470,16 +30678,8 @@
           <t xml:space="preserve">友達            </t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-41849</v>
       </c>
@@ -31503,16 +30703,8 @@
           <t xml:space="preserve">長興            </t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>79.90</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-24080</v>
       </c>
@@ -31536,16 +30728,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>25.99</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-20286</v>
       </c>
@@ -31569,16 +30753,8 @@
           <t xml:space="preserve">華航            </t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>18.10</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-15503</v>
       </c>
@@ -31602,16 +30778,8 @@
           <t xml:space="preserve">大同            </t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>31.70</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-14212</v>
       </c>
@@ -31635,16 +30803,8 @@
           <t xml:space="preserve">亞泥            </t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-11869</v>
       </c>
@@ -31668,16 +30828,8 @@
           <t xml:space="preserve">華通            </t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>250.50</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-10188</v>
       </c>
@@ -31701,16 +30853,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>41.47</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>+0.49</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-9595</v>
       </c>
@@ -31734,16 +30878,8 @@
           <t xml:space="preserve">大成鋼          </t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-9541</v>
       </c>
@@ -31767,16 +30903,8 @@
           <t xml:space="preserve">聯茂            </t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>282.00</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>+11.5</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-9073</v>
       </c>
@@ -31800,16 +30928,8 @@
           <t xml:space="preserve">國泰金          </t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>74.60</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-8345</v>
       </c>
@@ -31833,16 +30953,8 @@
           <t xml:space="preserve">定穎投控        </t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>190.50</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-7.5</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-8252</v>
       </c>
@@ -31866,16 +30978,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>12.62</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-7986</v>
       </c>
@@ -31899,16 +31003,8 @@
           <t xml:space="preserve">中工            </t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>13.70</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-7643</v>
       </c>
@@ -31932,16 +31028,8 @@
           <t xml:space="preserve">啟碁            </t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>251.50</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>-13.0</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-7494</v>
       </c>
@@ -31965,16 +31053,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>84.55</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-7141</v>
       </c>
@@ -31998,16 +31078,8 @@
           <t xml:space="preserve">寶成            </t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>27.50</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-6831</v>
       </c>
@@ -32031,16 +31103,8 @@
           <t xml:space="preserve">至上            </t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>85.50</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-1.7</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-6786</v>
       </c>
@@ -32064,16 +31128,8 @@
           <t xml:space="preserve">毅嘉            </t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>77.30</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-6458</v>
       </c>
@@ -32097,16 +31153,8 @@
           <t xml:space="preserve">國喬            </t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>13.30</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-6164</v>
       </c>
@@ -32130,16 +31178,8 @@
           <t xml:space="preserve">強茂            </t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-6021</v>
       </c>
@@ -32163,16 +31203,8 @@
           <t xml:space="preserve">陽明            </t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>50.10</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-5954</v>
       </c>
@@ -32196,16 +31228,8 @@
           <t xml:space="preserve">TPK-KY          </t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>71.20</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-5568</v>
       </c>
@@ -32229,16 +31253,8 @@
           <t xml:space="preserve">富邦金          </t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>87.20</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-5558</v>
       </c>
@@ -32262,16 +31278,8 @@
           <t xml:space="preserve">台中銀          </t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>20.50</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-5483</v>
       </c>
@@ -32295,16 +31303,8 @@
           <t xml:space="preserve">康舒            </t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-5211</v>
       </c>
@@ -32328,16 +31328,8 @@
           <t xml:space="preserve">旺宏            </t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>120.50</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>-10.5</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-5186</v>
       </c>
@@ -32361,16 +31353,8 @@
           <t xml:space="preserve">凌陽            </t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>24.20</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-5157</v>
       </c>
@@ -32394,16 +31378,8 @@
           <t xml:space="preserve">GIS-KY          </t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>83.80</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-4915</v>
       </c>
@@ -32427,16 +31403,8 @@
           <t xml:space="preserve">永豐金          </t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>32.20</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-4750</v>
       </c>
@@ -32460,16 +31428,8 @@
           <t xml:space="preserve">中鼎            </t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>36.40</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-4666</v>
       </c>
@@ -32493,16 +31453,8 @@
           <t xml:space="preserve">仁寶            </t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>30.25</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-4587</v>
       </c>
@@ -32526,16 +31478,8 @@
           <t xml:space="preserve">遠東新          </t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-4387</v>
       </c>
@@ -32559,16 +31503,8 @@
           <t xml:space="preserve">京元電子        </t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>271.00</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-4136</v>
       </c>
@@ -32592,16 +31528,8 @@
           <t xml:space="preserve">光罩            </t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>49.90</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-3398</v>
       </c>
@@ -32625,16 +31553,8 @@
           <t xml:space="preserve">仲琦            </t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>34.65</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-3153</v>
       </c>
@@ -32658,16 +31578,8 @@
           <t xml:space="preserve">凱基金          </t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>20.80</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-3145</v>
       </c>
@@ -32691,16 +31603,8 @@
           <t xml:space="preserve">威盛            </t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>66.20</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-3117</v>
       </c>
@@ -32724,16 +31628,8 @@
           <t xml:space="preserve">興富發          </t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>34.25</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-2955</v>
       </c>
@@ -32757,16 +31653,8 @@
           <t xml:space="preserve">致茂            </t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>2,050.00</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>-205.0</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-2939</v>
       </c>
@@ -32790,16 +31678,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>107.40</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-2735</v>
       </c>
@@ -32823,16 +31703,8 @@
           <t xml:space="preserve">眾達-KY         </t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>241.50</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-2693</v>
       </c>
@@ -32856,16 +31728,8 @@
           <t xml:space="preserve">臻鼎-KY         </t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>310.00</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>+28.0</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-2591</v>
       </c>
@@ -32889,16 +31753,8 @@
           <t xml:space="preserve">台塑            </t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>52.60</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-2573</v>
       </c>
@@ -32922,16 +31778,8 @@
           <t xml:space="preserve">楠梓電          </t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>112.00</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-2499</v>
       </c>
@@ -32955,16 +31803,8 @@
           <t xml:space="preserve">嘉聯益          </t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>18.80</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-2463</v>
       </c>
@@ -32988,16 +31828,8 @@
           <t xml:space="preserve">台積電          </t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>2,025.00</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-2460</v>
       </c>
@@ -33021,16 +31853,8 @@
           <t xml:space="preserve">台塑化          </t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>54.00</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-2405</v>
       </c>
@@ -33054,16 +31878,8 @@
           <t xml:space="preserve">南亞            </t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>85.70</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-2385</v>
       </c>
@@ -33155,16 +31971,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>24.51</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="D164" s="4" t="inlineStr"/>
+      <c r="E164" s="4" t="inlineStr"/>
       <c r="F164" s="4" t="n">
         <v>95037</v>
       </c>
@@ -33184,16 +31992,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>23.67</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>+0.24</t>
-        </is>
-      </c>
+      <c r="D165" s="4" t="inlineStr"/>
+      <c r="E165" s="4" t="inlineStr"/>
       <c r="F165" s="4" t="n">
         <v>84602</v>
       </c>
@@ -33213,16 +32013,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>10.34</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>+0.04</t>
-        </is>
-      </c>
+      <c r="D166" s="4" t="inlineStr"/>
+      <c r="E166" s="4" t="inlineStr"/>
       <c r="F166" s="4" t="n">
         <v>76487</v>
       </c>
@@ -33242,16 +32034,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>+0.42</t>
-        </is>
-      </c>
+      <c r="D167" s="4" t="inlineStr"/>
+      <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="n">
         <v>47209</v>
       </c>
@@ -33271,16 +32055,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>23.54</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>+0.13</t>
-        </is>
-      </c>
+      <c r="D168" s="4" t="inlineStr"/>
+      <c r="E168" s="4" t="inlineStr"/>
       <c r="F168" s="4" t="n">
         <v>34633</v>
       </c>
@@ -33300,16 +32076,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>9.03</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="D169" s="4" t="inlineStr"/>
+      <c r="E169" s="4" t="inlineStr"/>
       <c r="F169" s="4" t="n">
         <v>22452</v>
       </c>
@@ -33329,16 +32097,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>X0.0</t>
-        </is>
-      </c>
+      <c r="D170" s="4" t="inlineStr"/>
+      <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="n">
         <v>21895</v>
       </c>
@@ -33358,16 +32118,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>54.20</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="D171" s="4" t="inlineStr"/>
+      <c r="E171" s="4" t="inlineStr"/>
       <c r="F171" s="4" t="n">
         <v>13840</v>
       </c>
@@ -33387,16 +32139,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>+0.36</t>
-        </is>
-      </c>
+      <c r="D172" s="4" t="inlineStr"/>
+      <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="n">
         <v>11527</v>
       </c>
@@ -33416,16 +32160,8 @@
           <t>統一台灣高息動能</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>16.70</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="D173" s="4" t="inlineStr"/>
+      <c r="E173" s="4" t="inlineStr"/>
       <c r="F173" s="4" t="n">
         <v>10980</v>
       </c>
@@ -33518,16 +32254,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>25.99</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="D179" s="4" t="inlineStr"/>
+      <c r="E179" s="4" t="inlineStr"/>
       <c r="F179" s="4" t="n">
         <v>-20286</v>
       </c>
@@ -33547,16 +32275,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>41.47</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>+0.49</t>
-        </is>
-      </c>
+      <c r="D180" s="4" t="inlineStr"/>
+      <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="n">
         <v>-9595</v>
       </c>
@@ -33576,16 +32296,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>12.62</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
+      <c r="D181" s="4" t="inlineStr"/>
+      <c r="E181" s="4" t="inlineStr"/>
       <c r="F181" s="4" t="n">
         <v>-7986</v>
       </c>
@@ -33605,16 +32317,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>84.55</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="D182" s="4" t="inlineStr"/>
+      <c r="E182" s="4" t="inlineStr"/>
       <c r="F182" s="4" t="n">
         <v>-7141</v>
       </c>
@@ -33634,16 +32338,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>107.40</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="D183" s="4" t="inlineStr"/>
+      <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="n">
         <v>-2735</v>
       </c>
@@ -33663,16 +32359,8 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>9.66</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>+0.01</t>
-        </is>
-      </c>
+      <c r="D184" s="4" t="inlineStr"/>
+      <c r="E184" s="4" t="inlineStr"/>
       <c r="F184" s="4" t="n">
         <v>-1145</v>
       </c>
@@ -33692,16 +32380,8 @@
           <t xml:space="preserve">元大S&amp;P500      </t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>70.05</t>
-        </is>
-      </c>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="D185" s="4" t="inlineStr"/>
+      <c r="E185" s="4" t="inlineStr"/>
       <c r="F185" s="4" t="n">
         <v>-266</v>
       </c>

--- a/StockInfo/tse_analysis_result.xlsx
+++ b/StockInfo/tse_analysis_result.xlsx
@@ -28006,11 +28006,7 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>66505</v>
@@ -28035,16 +28031,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>10.24</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>59390</v>
       </c>
@@ -28068,16 +28056,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>40.90</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>49916</v>
       </c>
@@ -28101,16 +28081,8 @@
           <t xml:space="preserve">南亞科          </t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>226.50</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+20.5</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>38583</v>
       </c>
@@ -28134,16 +28106,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>23.33</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>35442</v>
       </c>
@@ -28167,16 +28131,8 @@
           <t xml:space="preserve">旺宏            </t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>145.00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+13.0</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>31899</v>
       </c>
@@ -28200,16 +28156,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>9.06</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>31713</v>
       </c>
@@ -28233,16 +28181,8 @@
           <t xml:space="preserve">華邦電          </t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>93.90</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+5.7</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>30707</v>
       </c>
@@ -28266,16 +28206,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>22.17</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>25269</v>
       </c>
@@ -28299,16 +28231,8 @@
           <t xml:space="preserve">鴻海            </t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>228.00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>24483</v>
       </c>
@@ -28332,16 +28256,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>23.23</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>16949</v>
       </c>
@@ -28365,16 +28281,8 @@
           <t xml:space="preserve">群創            </t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>24.30</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>13589</v>
       </c>
@@ -28398,16 +28306,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>53.10</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>11673</v>
       </c>
@@ -28431,16 +28331,8 @@
           <t xml:space="preserve">力積電          </t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>54.50</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>11368</v>
       </c>
@@ -28464,16 +28356,8 @@
           <t xml:space="preserve">南亞            </t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>87.80</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>10066</v>
       </c>
@@ -28497,16 +28381,8 @@
           <t xml:space="preserve">泰鼎-KY         </t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>58.60</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+5.3</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>10021</v>
       </c>
@@ -28530,16 +28406,8 @@
           <t xml:space="preserve">冠軍            </t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>8.08</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>9902</v>
       </c>
@@ -28563,16 +28431,8 @@
           <t xml:space="preserve">台化            </t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>50.40</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>9562</v>
       </c>
@@ -28596,16 +28456,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>15.25</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>8795</v>
       </c>
@@ -28629,16 +28481,8 @@
           <t xml:space="preserve">凱基金          </t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>20.50</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>8748</v>
       </c>
@@ -28662,16 +28506,8 @@
           <t xml:space="preserve">緯創            </t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>142.50</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>7466</v>
       </c>
@@ -28695,16 +28531,8 @@
           <t xml:space="preserve">三商壽          </t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>7.85</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+0.03</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>6031</v>
       </c>
@@ -28728,16 +28556,8 @@
           <t xml:space="preserve">光寶科          </t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>172.00</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>5909</v>
       </c>
@@ -28761,16 +28581,8 @@
           <t xml:space="preserve">至上            </t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>89.10</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+6.7</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>5823</v>
       </c>
@@ -28794,16 +28606,8 @@
           <t xml:space="preserve">中信中國高股息  </t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>15.63</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>5094</v>
       </c>
@@ -28827,16 +28631,8 @@
           <t xml:space="preserve">兆豐金          </t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>39.80</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>4441</v>
       </c>
@@ -28860,16 +28656,8 @@
           <t xml:space="preserve">台橡            </t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>20.40</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+1.85</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>4371</v>
       </c>
@@ -28893,11 +28681,7 @@
           <t xml:space="preserve">玉山金          </t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>32.55</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>4338</v>
@@ -28922,16 +28706,8 @@
           <t xml:space="preserve">華紙            </t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>13.25</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>4319</v>
       </c>
@@ -28955,16 +28731,8 @@
           <t xml:space="preserve">國巨*           </t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>305.00</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>4068</v>
       </c>
@@ -28988,16 +28756,8 @@
           <t xml:space="preserve">中石化          </t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>7.38</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>3754</v>
       </c>
@@ -29021,16 +28781,8 @@
           <t>統一台灣高息動能</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>16.56</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>3694</v>
       </c>
@@ -29054,16 +28806,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>34.54</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+0.87</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>3524</v>
       </c>
@@ -29087,16 +28831,8 @@
           <t xml:space="preserve">威健            </t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>35.65</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>3374</v>
       </c>
@@ -29120,11 +28856,7 @@
           <t xml:space="preserve">王道銀行        </t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>10.05</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>3313</v>
@@ -29149,16 +28881,8 @@
           <t xml:space="preserve">統一FANG+       </t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>120.20</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>3310</v>
       </c>
@@ -29182,16 +28906,8 @@
           <t xml:space="preserve">華新            </t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>2788</v>
       </c>
@@ -29215,16 +28931,8 @@
           <t xml:space="preserve">萬海            </t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>74.60</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>2738</v>
       </c>
@@ -29248,16 +28956,8 @@
           <t xml:space="preserve">技嘉            </t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>285.00</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>2490</v>
       </c>
@@ -29281,11 +28981,7 @@
           <t xml:space="preserve">東元            </t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>61.00</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>2436</v>
@@ -29310,16 +29006,8 @@
           <t xml:space="preserve">富邦台50        </t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>215.45</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>2319</v>
       </c>
@@ -29343,16 +29031,8 @@
           <t xml:space="preserve">國票金          </t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>2292</v>
       </c>
@@ -29376,16 +29056,8 @@
           <t xml:space="preserve">永豐金          </t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>2273</v>
       </c>
@@ -29409,16 +29081,8 @@
           <t xml:space="preserve">國建            </t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>26.55</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>2238</v>
       </c>
@@ -29442,16 +29106,8 @@
           <t xml:space="preserve">皇昌            </t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>46.35</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>1930</v>
       </c>
@@ -29475,16 +29131,8 @@
           <t xml:space="preserve">台聚            </t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>13.75</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>1820</v>
       </c>
@@ -29508,16 +29156,8 @@
           <t xml:space="preserve">亞聚            </t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>1710</v>
       </c>
@@ -29541,16 +29181,8 @@
           <t xml:space="preserve">矽力*-KY        </t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>420.00</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>-16.0</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>1657</v>
       </c>
@@ -29574,16 +29206,8 @@
           <t xml:space="preserve">研華            </t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>363.00</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>1515</v>
       </c>
@@ -29607,16 +29231,8 @@
           <t xml:space="preserve">燁輝            </t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>14.20</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>1482</v>
       </c>
@@ -29640,16 +29256,8 @@
           <t xml:space="preserve">神基            </t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>97.00</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>1482</v>
       </c>
@@ -29673,16 +29281,8 @@
           <t xml:space="preserve">菱生            </t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>1429</v>
       </c>
@@ -29706,16 +29306,8 @@
           <t xml:space="preserve">聯茂            </t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>265.00</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>1404</v>
       </c>
@@ -29739,16 +29331,8 @@
           <t xml:space="preserve">十銓            </t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>284.00</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+25.5</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>1359</v>
       </c>
@@ -29772,16 +29356,8 @@
           <t xml:space="preserve">台塑            </t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>50.30</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>1344</v>
       </c>
@@ -29805,16 +29381,8 @@
           <t xml:space="preserve">永光            </t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>51.20</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>1228</v>
       </c>
@@ -29838,16 +29406,8 @@
           <t xml:space="preserve">晶技            </t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>1219</v>
       </c>
@@ -29871,16 +29431,8 @@
           <t xml:space="preserve">華夏            </t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>14.20</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>1204</v>
       </c>
@@ -29904,16 +29456,8 @@
           <t xml:space="preserve">富世達          </t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>2,070.00</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+155.0</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>1176</v>
       </c>
@@ -29937,16 +29481,8 @@
           <t xml:space="preserve">艾笛森          </t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>22.30</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>1111</v>
       </c>
@@ -29970,16 +29506,8 @@
           <t xml:space="preserve">富邦金          </t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>87.90</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>1101</v>
       </c>
@@ -30003,16 +29531,8 @@
           <t xml:space="preserve">康舒            </t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>46.65</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>1076</v>
       </c>
@@ -30036,16 +29556,8 @@
           <t xml:space="preserve">百一            </t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>13.60</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>1063</v>
       </c>
@@ -30069,16 +29581,8 @@
           <t xml:space="preserve">瀚荃            </t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>116.50</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>1019</v>
       </c>
@@ -30102,16 +29606,8 @@
           <t xml:space="preserve">增你強          </t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>68.60</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>1017</v>
       </c>
@@ -30135,16 +29631,8 @@
           <t xml:space="preserve">欣興            </t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>839.00</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+49.0</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>1017</v>
       </c>
@@ -30168,16 +29656,8 @@
           <t xml:space="preserve">中鼎            </t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>36.40</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>1006</v>
       </c>
@@ -30201,16 +29681,8 @@
           <t xml:space="preserve">敬鵬            </t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>53.80</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>998</v>
       </c>
@@ -30234,16 +29706,8 @@
           <t xml:space="preserve">和桐            </t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>9.67</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+0.04</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>993</v>
       </c>
@@ -30267,16 +29731,8 @@
           <t xml:space="preserve">富邦公司治理    </t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>81.10</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>992</v>
       </c>
@@ -30300,16 +29756,8 @@
           <t xml:space="preserve">元晶            </t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>37.45</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>987</v>
       </c>
@@ -30333,16 +29781,8 @@
           <t xml:space="preserve">華南金          </t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>35.25</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>977</v>
       </c>
@@ -30366,16 +29806,8 @@
           <t xml:space="preserve">中再保          </t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>30.20</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>958</v>
       </c>
@@ -30399,16 +29831,8 @@
           <t xml:space="preserve">台塑化          </t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>51.80</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>936</v>
       </c>
@@ -30432,16 +29856,8 @@
           <t xml:space="preserve">台船            </t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>921</v>
       </c>
@@ -30465,16 +29881,8 @@
           <t xml:space="preserve">泰碩            </t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>78.50</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-2.7</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>898</v>
       </c>
@@ -30498,11 +29906,7 @@
           <t xml:space="preserve">聯發科          </t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>2,435.00</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>871</v>
@@ -30527,16 +29931,8 @@
           <t xml:space="preserve">統新            </t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>205.00</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>851</v>
       </c>
@@ -30560,16 +29956,8 @@
           <t xml:space="preserve">GIS-KY          </t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>72.70</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>848</v>
       </c>
@@ -30593,16 +29981,8 @@
           <t xml:space="preserve">恩德            </t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>24.90</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>827</v>
       </c>
@@ -30626,16 +30006,8 @@
           <t xml:space="preserve">瑞昱            </t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>555.00</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+16.0</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>822</v>
       </c>
@@ -30659,16 +30031,8 @@
           <t xml:space="preserve">南茂            </t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>67.80</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>794</v>
       </c>
@@ -30692,16 +30056,8 @@
           <t xml:space="preserve">眾達-KY         </t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>205.00</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>-10.5</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>789</v>
       </c>
@@ -30725,16 +30081,8 @@
           <t xml:space="preserve">台苯            </t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>9.51</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>787</v>
       </c>
@@ -30758,16 +30106,8 @@
           <t xml:space="preserve">中磊            </t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>77.40</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>780</v>
       </c>
@@ -30791,16 +30131,8 @@
           <t xml:space="preserve">裕融            </t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>78.70</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>777</v>
       </c>
@@ -30824,11 +30156,7 @@
           <t xml:space="preserve">強盛新          </t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
       <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>762</v>
@@ -30853,16 +30181,8 @@
           <t xml:space="preserve">文曄            </t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>201.00</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>761</v>
       </c>
@@ -30886,16 +30206,8 @@
           <t xml:space="preserve">晶豪科          </t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>168.00</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+13.5</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>750</v>
       </c>
@@ -30919,16 +30231,8 @@
           <t xml:space="preserve">勝一            </t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>179.00</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>742</v>
       </c>
@@ -30952,16 +30256,8 @@
           <t xml:space="preserve">統一證          </t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>35.70</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>726</v>
       </c>
@@ -30985,16 +30281,8 @@
           <t xml:space="preserve">上曜            </t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>10.90</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>715</v>
       </c>
@@ -31018,16 +30306,8 @@
           <t xml:space="preserve">台達化          </t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>694</v>
       </c>
@@ -31051,16 +30331,8 @@
           <t xml:space="preserve">東聯            </t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>686</v>
       </c>
@@ -31084,16 +30356,8 @@
           <t xml:space="preserve">佳能            </t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>70.90</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>679</v>
       </c>
@@ -31117,16 +30381,8 @@
           <t xml:space="preserve">鈞寶            </t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>47.30</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+4.3</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>670</v>
       </c>
@@ -31150,16 +30406,8 @@
           <t xml:space="preserve">精英            </t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>644</v>
       </c>
@@ -31183,16 +30431,8 @@
           <t xml:space="preserve">誠美材          </t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>37.40</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>632</v>
       </c>
@@ -31216,16 +30456,8 @@
           <t xml:space="preserve">台汽電          </t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>598</v>
       </c>
@@ -31249,16 +30481,8 @@
           <t xml:space="preserve">台郡            </t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>65.40</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>597</v>
       </c>
@@ -31359,16 +30583,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>29.62</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>+1.18</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-148434</v>
       </c>
@@ -31392,16 +30608,8 @@
           <t xml:space="preserve">中鋼            </t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-38692</v>
       </c>
@@ -31425,16 +30633,8 @@
           <t xml:space="preserve">友達            </t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>17.35</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-37039</v>
       </c>
@@ -31458,16 +30658,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>11.71</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-36938</v>
       </c>
@@ -31491,16 +30683,8 @@
           <t xml:space="preserve">聯電            </t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>72.70</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-36262</v>
       </c>
@@ -31524,16 +30708,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>93.00</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>+3.05</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-23923</v>
       </c>
@@ -31557,16 +30733,8 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-22758</v>
       </c>
@@ -31590,16 +30758,8 @@
           <t xml:space="preserve">英業達          </t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>46.70</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-14939</v>
       </c>
@@ -31623,16 +30783,8 @@
           <t xml:space="preserve">台積電          </t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>2,265.00</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>+80.0</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-13408</v>
       </c>
@@ -31656,16 +30808,8 @@
           <t xml:space="preserve">中信金          </t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>52.70</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-10569</v>
       </c>
@@ -31689,16 +30833,8 @@
           <t xml:space="preserve">國泰金          </t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>74.50</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-10041</v>
       </c>
@@ -31722,16 +30858,8 @@
           <t xml:space="preserve">群益證          </t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>27.95</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-9618</v>
       </c>
@@ -31755,16 +30883,8 @@
           <t xml:space="preserve">景碩            </t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>515.00</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-9409</v>
       </c>
@@ -31788,16 +30908,8 @@
           <t xml:space="preserve">長榮航          </t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>33.35</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-9257</v>
       </c>
@@ -31821,16 +30933,8 @@
           <t xml:space="preserve">智原            </t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>186.50</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-8558</v>
       </c>
@@ -31854,16 +30958,8 @@
           <t xml:space="preserve">仁寶            </t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-7650</v>
       </c>
@@ -31887,16 +30983,8 @@
           <t xml:space="preserve">臺企銀          </t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>16.15</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-6845</v>
       </c>
@@ -31920,16 +31008,8 @@
           <t xml:space="preserve">兆赫            </t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>62.20</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-6782</v>
       </c>
@@ -31953,16 +31033,8 @@
           <t xml:space="preserve">昇陽半導體      </t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>229.50</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-12.5</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-6548</v>
       </c>
@@ -31986,16 +31058,8 @@
           <t xml:space="preserve">上海商銀        </t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-6349</v>
       </c>
@@ -32019,16 +31083,8 @@
           <t xml:space="preserve">華航            </t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>17.80</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-6135</v>
       </c>
@@ -32052,16 +31108,8 @@
           <t xml:space="preserve">台中銀          </t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>19.80</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-5766</v>
       </c>
@@ -32085,16 +31133,8 @@
           <t xml:space="preserve">合庫金          </t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>22.90</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-5499</v>
       </c>
@@ -32118,16 +31158,8 @@
           <t xml:space="preserve">寶成            </t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>26.20</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-5487</v>
       </c>
@@ -32151,16 +31183,8 @@
           <t xml:space="preserve">臻鼎-KY         </t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>358.50</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-5380</v>
       </c>
@@ -32184,16 +31208,8 @@
           <t xml:space="preserve">台泥            </t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>24.35</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-5166</v>
       </c>
@@ -32217,16 +31233,8 @@
           <t xml:space="preserve">燿華            </t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>59.80</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>+2.4</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-5163</v>
       </c>
@@ -32250,16 +31258,8 @@
           <t xml:space="preserve">台新新光金      </t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-5149</v>
       </c>
@@ -32283,16 +31283,8 @@
           <t xml:space="preserve">宏碁            </t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>27.20</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-5143</v>
       </c>
@@ -32316,16 +31308,8 @@
           <t xml:space="preserve">日月光投控      </t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>495.50</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-4718</v>
       </c>
@@ -32349,16 +31333,8 @@
           <t xml:space="preserve">瑞儀            </t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-4521</v>
       </c>
@@ -32382,16 +31358,8 @@
           <t xml:space="preserve">映泰            </t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>41.35</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-2.3</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-4388</v>
       </c>
@@ -32415,16 +31383,8 @@
           <t xml:space="preserve">南電            </t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>913.00</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>+39.0</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-4097</v>
       </c>
@@ -32448,16 +31408,8 @@
           <t xml:space="preserve">中華電          </t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>137.00</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-3886</v>
       </c>
@@ -32481,16 +31433,8 @@
           <t xml:space="preserve">台達電          </t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>2,020.00</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>-55.0</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-3794</v>
       </c>
@@ -32514,16 +31458,8 @@
           <t xml:space="preserve">遠東銀          </t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>12.25</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-3742</v>
       </c>
@@ -32547,16 +31483,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>110.45</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>+1.35</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-3737</v>
       </c>
@@ -32580,16 +31508,8 @@
           <t xml:space="preserve">矽格            </t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>178.00</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-3625</v>
       </c>
@@ -32613,16 +31533,8 @@
           <t xml:space="preserve">統一            </t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>70.50</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-3474</v>
       </c>
@@ -32646,16 +31558,8 @@
           <t xml:space="preserve">全新            </t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>311.50</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-34.5</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-3441</v>
       </c>
@@ -32679,16 +31583,8 @@
           <t xml:space="preserve">盟立            </t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>97.00</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>+5.3</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-3116</v>
       </c>
@@ -32712,16 +31608,8 @@
           <t xml:space="preserve">亞泥            </t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>35.25</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-3100</v>
       </c>
@@ -32745,16 +31633,8 @@
           <t xml:space="preserve">台灣大          </t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>112.00</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-3067</v>
       </c>
@@ -32778,16 +31658,8 @@
           <t xml:space="preserve">彩晶            </t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>8.25</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-3027</v>
       </c>
@@ -32811,16 +31683,8 @@
           <t xml:space="preserve">威盛            </t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>74.70</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-2982</v>
       </c>
@@ -32844,16 +31708,8 @@
           <t xml:space="preserve">凌陽            </t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>23.00</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-2949</v>
       </c>
@@ -32877,16 +31733,8 @@
           <t xml:space="preserve">采鈺            </t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>557.00</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-9.0</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-2935</v>
       </c>
@@ -32910,16 +31758,8 @@
           <t xml:space="preserve">中租-KY         </t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>116.00</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-5.5</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-2731</v>
       </c>
@@ -32943,16 +31783,8 @@
           <t xml:space="preserve">正新            </t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>31.70</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-2716</v>
       </c>
@@ -32976,16 +31808,8 @@
           <t xml:space="preserve">陽明            </t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>49.35</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-2637</v>
       </c>
@@ -33077,11 +31901,7 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
-      </c>
+      <c r="D164" s="4" t="inlineStr"/>
       <c r="E164" s="4" t="inlineStr"/>
       <c r="F164" s="4" t="n">
         <v>66505</v>
@@ -33102,16 +31922,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>10.24</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
+      <c r="D165" s="4" t="inlineStr"/>
+      <c r="E165" s="4" t="inlineStr"/>
       <c r="F165" s="4" t="n">
         <v>59390</v>
       </c>
@@ -33131,16 +31943,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>40.90</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="D166" s="4" t="inlineStr"/>
+      <c r="E166" s="4" t="inlineStr"/>
       <c r="F166" s="4" t="n">
         <v>49916</v>
       </c>
@@ -33160,16 +31964,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>23.33</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
+      <c r="D167" s="4" t="inlineStr"/>
+      <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="n">
         <v>35442</v>
       </c>
@@ -33189,16 +31985,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>9.06</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="D168" s="4" t="inlineStr"/>
+      <c r="E168" s="4" t="inlineStr"/>
       <c r="F168" s="4" t="n">
         <v>31713</v>
       </c>
@@ -33218,16 +32006,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>22.17</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
+      <c r="D169" s="4" t="inlineStr"/>
+      <c r="E169" s="4" t="inlineStr"/>
       <c r="F169" s="4" t="n">
         <v>25269</v>
       </c>
@@ -33247,16 +32027,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>23.23</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
+      <c r="D170" s="4" t="inlineStr"/>
+      <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="n">
         <v>16949</v>
       </c>
@@ -33276,16 +32048,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>53.10</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="D171" s="4" t="inlineStr"/>
+      <c r="E171" s="4" t="inlineStr"/>
       <c r="F171" s="4" t="n">
         <v>11673</v>
       </c>
@@ -33305,16 +32069,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>15.25</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
+      <c r="D172" s="4" t="inlineStr"/>
+      <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="n">
         <v>8795</v>
       </c>
@@ -33334,16 +32090,8 @@
           <t xml:space="preserve">中信中國高股息  </t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>15.63</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
+      <c r="D173" s="4" t="inlineStr"/>
+      <c r="E173" s="4" t="inlineStr"/>
       <c r="F173" s="4" t="n">
         <v>5094</v>
       </c>
@@ -33436,16 +32184,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>29.62</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>+1.18</t>
-        </is>
-      </c>
+      <c r="D179" s="4" t="inlineStr"/>
+      <c r="E179" s="4" t="inlineStr"/>
       <c r="F179" s="4" t="n">
         <v>-148434</v>
       </c>
@@ -33465,16 +32205,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>11.71</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
+      <c r="D180" s="4" t="inlineStr"/>
+      <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="n">
         <v>-36938</v>
       </c>
@@ -33494,16 +32226,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>93.00</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>+3.05</t>
-        </is>
-      </c>
+      <c r="D181" s="4" t="inlineStr"/>
+      <c r="E181" s="4" t="inlineStr"/>
       <c r="F181" s="4" t="n">
         <v>-23923</v>
       </c>
@@ -33523,16 +32247,8 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
+      <c r="D182" s="4" t="inlineStr"/>
+      <c r="E182" s="4" t="inlineStr"/>
       <c r="F182" s="4" t="n">
         <v>-22758</v>
       </c>
@@ -33552,16 +32268,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>110.45</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>+1.35</t>
-        </is>
-      </c>
+      <c r="D183" s="4" t="inlineStr"/>
+      <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="n">
         <v>-3737</v>
       </c>
@@ -33581,16 +32289,8 @@
           <t>國泰台灣科技龍頭</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>46.99</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>+1.09</t>
-        </is>
-      </c>
+      <c r="D184" s="4" t="inlineStr"/>
+      <c r="E184" s="4" t="inlineStr"/>
       <c r="F184" s="4" t="n">
         <v>-1993</v>
       </c>
@@ -33610,16 +32310,8 @@
           <t xml:space="preserve">元大S&amp;P500      </t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>70.50</t>
-        </is>
-      </c>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="D185" s="4" t="inlineStr"/>
+      <c r="E185" s="4" t="inlineStr"/>
       <c r="F185" s="4" t="n">
         <v>-661</v>
       </c>

--- a/StockInfo/tse_analysis_result.xlsx
+++ b/StockInfo/tse_analysis_result.xlsx
@@ -28427,16 +28427,8 @@
           <t xml:space="preserve">友達            </t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>20.70</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+1.85</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>119357</v>
       </c>
@@ -28460,16 +28452,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>25.73</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>107078</v>
       </c>
@@ -28493,16 +28477,8 @@
           <t xml:space="preserve">群創            </t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>35.50</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+3.2</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>82769</v>
       </c>
@@ -28526,16 +28502,8 @@
           <t xml:space="preserve">聯電            </t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>104.50</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>50086</v>
       </c>
@@ -28559,16 +28527,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>11.27</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>37833</v>
       </c>
@@ -28592,16 +28552,8 @@
           <t xml:space="preserve">華邦電          </t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>121.50</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>34862</v>
       </c>
@@ -28625,16 +28577,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>25.49</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+0.11</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>33690</v>
       </c>
@@ -28658,16 +28602,8 @@
           <t xml:space="preserve">華通            </t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>260.00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+18.0</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>33551</v>
       </c>
@@ -28691,16 +28627,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>45.58</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>33231</v>
       </c>
@@ -28724,16 +28652,8 @@
           <t xml:space="preserve">南亞科          </t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>321.00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+20.0</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>28854</v>
       </c>
@@ -28757,16 +28677,8 @@
           <t xml:space="preserve">光寶科          </t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>234.50</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>21216</v>
       </c>
@@ -28790,16 +28702,8 @@
           <t xml:space="preserve">鴻海            </t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>21015</v>
       </c>
@@ -28823,16 +28727,8 @@
           <t xml:space="preserve">緯創            </t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>141.50</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>20204</v>
       </c>
@@ -28856,16 +28752,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>26.03</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+0.04</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>19867</v>
       </c>
@@ -28889,16 +28777,8 @@
           <t xml:space="preserve">彩晶            </t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>10.65</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+0.94</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>16641</v>
       </c>
@@ -28922,16 +28802,8 @@
           <t xml:space="preserve">強茂            </t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>115.50</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>15184</v>
       </c>
@@ -28955,16 +28827,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>28.13</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>14357</v>
       </c>
@@ -28988,16 +28852,8 @@
           <t xml:space="preserve">遠東新          </t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>26.65</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>13734</v>
       </c>
@@ -29021,16 +28877,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>54.80</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>13039</v>
       </c>
@@ -29054,16 +28902,8 @@
           <t xml:space="preserve">台玻            </t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>71.10</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>12468</v>
       </c>
@@ -29087,16 +28927,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>17.25</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>11453</v>
       </c>
@@ -29120,16 +28952,8 @@
           <t xml:space="preserve">和桐            </t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+0.44</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>10659</v>
       </c>
@@ -29153,16 +28977,8 @@
           <t xml:space="preserve">第一金          </t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>29.40</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>9736</v>
       </c>
@@ -29186,11 +29002,7 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>9.55</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>8568</v>
@@ -29215,16 +29027,8 @@
           <t xml:space="preserve">富采            </t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>73.70</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+5.8</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>8266</v>
       </c>
@@ -29248,16 +29052,8 @@
           <t xml:space="preserve">啟碁            </t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>282.00</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+23.0</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>7523</v>
       </c>
@@ -29281,16 +29077,8 @@
           <t xml:space="preserve">上海商銀        </t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>40.10</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>6306</v>
       </c>
@@ -29314,16 +29102,8 @@
           <t xml:space="preserve">長興            </t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>82.70</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>6005</v>
       </c>
@@ -29347,16 +29127,8 @@
           <t xml:space="preserve">聯鈞            </t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>470.50</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+42.5</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>5790</v>
       </c>
@@ -29380,16 +29152,8 @@
           <t xml:space="preserve">昇貿            </t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>128.50</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+11.5</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>5506</v>
       </c>
@@ -29413,16 +29177,8 @@
           <t xml:space="preserve">威健            </t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>5482</v>
       </c>
@@ -29446,16 +29202,8 @@
           <t xml:space="preserve">燿華            </t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>64.80</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>4936</v>
       </c>
@@ -29479,16 +29227,8 @@
           <t xml:space="preserve">佳能            </t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>82.40</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>4451</v>
       </c>
@@ -29512,16 +29252,8 @@
           <t>統一台灣高息動能</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>18.04</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>4429</v>
       </c>
@@ -29545,16 +29277,8 @@
           <t xml:space="preserve">中再保          </t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>34.10</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+2.55</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>4277</v>
       </c>
@@ -29578,16 +29302,8 @@
           <t xml:space="preserve">中石化          </t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>7.08</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>3984</v>
       </c>
@@ -29611,16 +29327,8 @@
           <t xml:space="preserve">益登            </t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>46.90</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>3908</v>
       </c>
@@ -29644,16 +29352,8 @@
           <t xml:space="preserve">宏達電          </t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>41.30</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>3445</v>
       </c>
@@ -29677,16 +29377,8 @@
           <t xml:space="preserve">欣興            </t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>875.00</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+14.0</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>3424</v>
       </c>
@@ -29710,16 +29402,8 @@
           <t xml:space="preserve">飛捷            </t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>3382</v>
       </c>
@@ -29743,16 +29427,8 @@
           <t xml:space="preserve">富邦台50        </t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>224.55</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>3200</v>
       </c>
@@ -29776,16 +29452,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>36.60</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>3179</v>
       </c>
@@ -29809,16 +29477,8 @@
           <t xml:space="preserve">大成鋼          </t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>39.70</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>3168</v>
       </c>
@@ -29842,16 +29502,8 @@
           <t xml:space="preserve">中信中國高股息  </t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>16.28</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+0.13</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>2980</v>
       </c>
@@ -29875,16 +29527,8 @@
           <t xml:space="preserve">聯詠            </t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>487.00</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>2961</v>
       </c>
@@ -29908,16 +29552,8 @@
           <t xml:space="preserve">技嘉            </t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>321.00</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>2934</v>
       </c>
@@ -29941,16 +29577,8 @@
           <t xml:space="preserve">康普            </t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>2853</v>
       </c>
@@ -29974,16 +29602,8 @@
           <t xml:space="preserve">佳世達          </t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>2851</v>
       </c>
@@ -30007,16 +29627,8 @@
           <t xml:space="preserve">凌巨            </t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>2837</v>
       </c>
@@ -30040,16 +29652,8 @@
           <t xml:space="preserve">日月光投控      </t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>555.00</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+18.0</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>2795</v>
       </c>
@@ -30073,16 +29677,8 @@
           <t>國泰台灣科技龍頭</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>50.95</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>2678</v>
       </c>
@@ -30106,16 +29702,8 @@
           <t xml:space="preserve">力積電          </t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>62.10</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>2550</v>
       </c>
@@ -30139,16 +29727,8 @@
           <t xml:space="preserve">廣達            </t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>340.00</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>2290</v>
       </c>
@@ -30172,16 +29752,8 @@
           <t xml:space="preserve">事欣科          </t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>68.40</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>2288</v>
       </c>
@@ -30205,16 +29777,8 @@
           <t xml:space="preserve">晶豪科          </t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>220.00</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>2009</v>
       </c>
@@ -30238,16 +29802,8 @@
           <t xml:space="preserve">統一            </t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>73.10</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>1970</v>
       </c>
@@ -30271,16 +29827,8 @@
           <t xml:space="preserve">茂矽            </t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>44.10</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>1896</v>
       </c>
@@ -30304,16 +29852,8 @@
           <t xml:space="preserve">東鹼            </t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>41.75</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>1882</v>
       </c>
@@ -30337,16 +29877,8 @@
           <t xml:space="preserve">合勤控          </t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>37.05</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>1862</v>
       </c>
@@ -30370,16 +29902,8 @@
           <t xml:space="preserve">上銀            </t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>367.50</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+16.5</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>1781</v>
       </c>
@@ -30403,16 +29927,8 @@
           <t xml:space="preserve">全新            </t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>375.00</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+15.0</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>1779</v>
       </c>
@@ -30436,16 +29952,8 @@
           <t xml:space="preserve">毅嘉            </t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>70.80</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+1.8</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>1720</v>
       </c>
@@ -30469,16 +29977,8 @@
           <t xml:space="preserve">台橡            </t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>21.30</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>1637</v>
       </c>
@@ -30502,16 +30002,8 @@
           <t xml:space="preserve">志聖            </t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>649.00</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+59.0</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>1571</v>
       </c>
@@ -30535,16 +30027,8 @@
           <t xml:space="preserve">正達            </t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>51.40</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>1550</v>
       </c>
@@ -30568,16 +30052,8 @@
           <t xml:space="preserve">康舒            </t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>56.00</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>1547</v>
       </c>
@@ -30601,16 +30077,8 @@
           <t xml:space="preserve">中鼎            </t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>37.10</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>1499</v>
       </c>
@@ -30634,16 +30102,8 @@
           <t xml:space="preserve">蔚華科          </t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>1450</v>
       </c>
@@ -30667,16 +30127,8 @@
           <t xml:space="preserve">映泰            </t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>46.45</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+1.65</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>1441</v>
       </c>
@@ -30700,16 +30152,8 @@
           <t xml:space="preserve">德淵            </t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>26.95</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>1433</v>
       </c>
@@ -30733,16 +30177,8 @@
           <t xml:space="preserve">國巨*           </t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>419.50</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+28.0</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>1324</v>
       </c>
@@ -30766,16 +30202,8 @@
           <t xml:space="preserve">華泰            </t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>1309</v>
       </c>
@@ -30799,16 +30227,8 @@
           <t xml:space="preserve">中釉            </t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>40.40</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>1293</v>
       </c>
@@ -30832,16 +30252,8 @@
           <t xml:space="preserve">宏全            </t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>122.50</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>1196</v>
       </c>
@@ -30865,11 +30277,7 @@
           <t xml:space="preserve">瑞儀            </t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>104.00</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>1196</v>
@@ -30894,16 +30302,8 @@
           <t xml:space="preserve">嘉聯益          </t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>18.45</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>1148</v>
       </c>
@@ -30927,16 +30327,8 @@
           <t xml:space="preserve">菱生            </t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>31.20</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>1123</v>
       </c>
@@ -30960,16 +30352,8 @@
           <t xml:space="preserve">全科            </t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>66.50</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>1098</v>
       </c>
@@ -30993,16 +30377,8 @@
           <t xml:space="preserve">大毅            </t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>80.00</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+2.1</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>1094</v>
       </c>
@@ -31026,16 +30402,8 @@
           <t xml:space="preserve">晶技            </t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>149.50</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>1065</v>
       </c>
@@ -31059,16 +30427,8 @@
           <t xml:space="preserve">達運            </t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>1062</v>
       </c>
@@ -31092,16 +30452,8 @@
           <t xml:space="preserve">神達            </t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>85.90</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>1056</v>
       </c>
@@ -31125,16 +30477,8 @@
           <t xml:space="preserve">南電            </t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>900.00</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>1054</v>
       </c>
@@ -31158,16 +30502,8 @@
           <t xml:space="preserve">中磊            </t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>88.20</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>1002</v>
       </c>
@@ -31191,16 +30527,8 @@
           <t xml:space="preserve">楠梓電          </t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>135.50</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>+12.0</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>1001</v>
       </c>
@@ -31224,16 +30552,8 @@
           <t xml:space="preserve">台亞            </t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>38.05</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>985</v>
       </c>
@@ -31257,16 +30577,8 @@
           <t xml:space="preserve">彰源            </t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>17.95</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>977</v>
       </c>
@@ -31290,16 +30602,8 @@
           <t xml:space="preserve">統一FANG+       </t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>127.25</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>928</v>
       </c>
@@ -31323,16 +30627,8 @@
           <t xml:space="preserve">全球傳動        </t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>68.90</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>921</v>
       </c>
@@ -31356,16 +30652,8 @@
           <t xml:space="preserve">興勤            </t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>201.50</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>899</v>
       </c>
@@ -31389,16 +30677,8 @@
           <t xml:space="preserve">和椿            </t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>126.00</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>860</v>
       </c>
@@ -31422,16 +30702,8 @@
           <t xml:space="preserve">全友            </t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>859</v>
       </c>
@@ -31455,16 +30727,8 @@
           <t xml:space="preserve">富邦公司治理    </t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>84.50</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>836</v>
       </c>
@@ -31488,16 +30752,8 @@
           <t xml:space="preserve">第一銅          </t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>40.90</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>835</v>
       </c>
@@ -31521,16 +30777,8 @@
           <t xml:space="preserve">國精化          </t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>258.50</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+23.5</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>802</v>
       </c>
@@ -31554,16 +30802,8 @@
           <t xml:space="preserve">凌陽            </t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>794</v>
       </c>
@@ -31587,16 +30827,8 @@
           <t xml:space="preserve">希華            </t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>38.90</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>779</v>
       </c>
@@ -31620,16 +30852,8 @@
           <t xml:space="preserve">鈺邦            </t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>198.50</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+18.0</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>761</v>
       </c>
@@ -31653,16 +30877,8 @@
           <t xml:space="preserve">台塑化          </t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>53.10</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>754</v>
       </c>
@@ -31686,16 +30902,8 @@
           <t xml:space="preserve">凌華            </t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>101.50</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+8.8</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>736</v>
       </c>
@@ -31796,16 +31004,8 @@
           <t xml:space="preserve">中信金          </t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>53.50</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-42346</v>
       </c>
@@ -31829,16 +31029,8 @@
           <t xml:space="preserve">台新新光金      </t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>23.00</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-32447</v>
       </c>
@@ -31862,16 +31054,8 @@
           <t xml:space="preserve">凱基金          </t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>21.60</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-31032</v>
       </c>
@@ -31895,16 +31079,8 @@
           <t xml:space="preserve">至上            </t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>81.80</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-25359</v>
       </c>
@@ -31928,16 +31104,8 @@
           <t xml:space="preserve">彰銀            </t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>20.60</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-23657</v>
       </c>
@@ -31961,16 +31129,8 @@
           <t xml:space="preserve">中鋼            </t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-21961</v>
       </c>
@@ -31994,16 +31154,8 @@
           <t xml:space="preserve">臺企銀          </t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>16.00</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-21188</v>
       </c>
@@ -32027,16 +31179,8 @@
           <t xml:space="preserve">旺宏            </t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>153.00</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-6.5</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-20580</v>
       </c>
@@ -32060,16 +31204,8 @@
           <t xml:space="preserve">仁寶            </t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>29.90</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-18412</v>
       </c>
@@ -32093,16 +31229,8 @@
           <t xml:space="preserve">玉山金          </t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>31.80</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-17571</v>
       </c>
@@ -32126,16 +31254,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>11.21</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-17439</v>
       </c>
@@ -32159,16 +31279,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>96.85</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-15923</v>
       </c>
@@ -32192,16 +31304,8 @@
           <t xml:space="preserve">長榮航          </t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>35.10</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-15840</v>
       </c>
@@ -32225,16 +31329,8 @@
           <t xml:space="preserve">台塑            </t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>47.65</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-15408</v>
       </c>
@@ -32258,16 +31354,8 @@
           <t xml:space="preserve">合庫金          </t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>22.80</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-14500</v>
       </c>
@@ -32291,16 +31379,8 @@
           <t xml:space="preserve">京元電子        </t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>301.00</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-13801</v>
       </c>
@@ -32324,16 +31404,8 @@
           <t xml:space="preserve">華航            </t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-12963</v>
       </c>
@@ -32357,16 +31429,8 @@
           <t xml:space="preserve">元大金          </t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>54.60</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-12955</v>
       </c>
@@ -32390,16 +31454,8 @@
           <t xml:space="preserve">國泰金          </t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>76.40</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-12395</v>
       </c>
@@ -32423,16 +31479,8 @@
           <t xml:space="preserve">台泥            </t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>24.95</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-11869</v>
       </c>
@@ -32456,16 +31504,8 @@
           <t xml:space="preserve">南亞            </t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>89.10</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-11348</v>
       </c>
@@ -32489,16 +31529,8 @@
           <t xml:space="preserve">華南金          </t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>32.55</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-9733</v>
       </c>
@@ -32522,16 +31554,8 @@
           <t xml:space="preserve">兆豐金          </t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>39.20</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-8808</v>
       </c>
@@ -32555,16 +31579,8 @@
           <t xml:space="preserve">金寶            </t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-8598</v>
       </c>
@@ -32588,16 +31604,8 @@
           <t xml:space="preserve">微星            </t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>105.00</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-8557</v>
       </c>
@@ -32621,16 +31629,8 @@
           <t xml:space="preserve">富邦金          </t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>93.70</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-8262</v>
       </c>
@@ -32654,16 +31654,8 @@
           <t xml:space="preserve">英業達          </t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>48.70</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-7572</v>
       </c>
@@ -32687,16 +31679,8 @@
           <t xml:space="preserve">台中銀          </t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>19.60</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-6679</v>
       </c>
@@ -32720,16 +31704,8 @@
           <t xml:space="preserve">新唐            </t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>181.00</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-6658</v>
       </c>
@@ -32753,16 +31729,8 @@
           <t xml:space="preserve">宏碁            </t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>28.30</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-6524</v>
       </c>
@@ -32786,16 +31754,8 @@
           <t xml:space="preserve">大同            </t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>30.10</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-6179</v>
       </c>
@@ -32819,16 +31779,8 @@
           <t xml:space="preserve">統一證          </t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>41.80</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-6112</v>
       </c>
@@ -32852,16 +31804,8 @@
           <t xml:space="preserve">聯茂            </t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>285.50</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-6022</v>
       </c>
@@ -32885,16 +31829,8 @@
           <t xml:space="preserve">和碩            </t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>81.10</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-2.3</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-5580</v>
       </c>
@@ -32918,16 +31854,8 @@
           <t xml:space="preserve">南茂            </t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>87.00</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-4850</v>
       </c>
@@ -32951,16 +31879,8 @@
           <t xml:space="preserve">正文            </t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>39.50</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-4573</v>
       </c>
@@ -32984,16 +31904,8 @@
           <t xml:space="preserve">台達電          </t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>2,195.00</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-4282</v>
       </c>
@@ -33017,16 +31929,8 @@
           <t xml:space="preserve">台表科          </t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>214.50</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-4222</v>
       </c>
@@ -33050,16 +31954,8 @@
           <t xml:space="preserve">中租-KY         </t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>109.50</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-3880</v>
       </c>
@@ -33083,16 +31979,8 @@
           <t xml:space="preserve">正新            </t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-3613</v>
       </c>
@@ -33116,16 +32004,8 @@
           <t xml:space="preserve">寶成            </t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-3494</v>
       </c>
@@ -33149,16 +32029,8 @@
           <t xml:space="preserve">臻鼎-KY         </t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>407.00</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-3434</v>
       </c>
@@ -33182,16 +32054,8 @@
           <t xml:space="preserve">工信            </t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>11.50</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-3334</v>
       </c>
@@ -33215,16 +32079,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>118.05</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-3245</v>
       </c>
@@ -33248,16 +32104,8 @@
           <t xml:space="preserve">潤泰新          </t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-3106</v>
       </c>
@@ -33281,16 +32129,8 @@
           <t xml:space="preserve">陽明            </t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>50.10</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-2955</v>
       </c>
@@ -33314,16 +32154,8 @@
           <t xml:space="preserve">偉詮電          </t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>76.60</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-2950</v>
       </c>
@@ -33347,16 +32179,8 @@
           <t xml:space="preserve">宇瞻            </t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-2849</v>
       </c>
@@ -33380,16 +32204,8 @@
           <t xml:space="preserve">誠美材          </t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>38.15</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-2809</v>
       </c>
@@ -33413,16 +32229,8 @@
           <t xml:space="preserve">瑞軒            </t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>41.80</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-2801</v>
       </c>
@@ -33514,16 +32322,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>25.73</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
+      <c r="D164" s="4" t="inlineStr"/>
+      <c r="E164" s="4" t="inlineStr"/>
       <c r="F164" s="4" t="n">
         <v>107078</v>
       </c>
@@ -33543,16 +32343,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>11.27</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
+      <c r="D165" s="4" t="inlineStr"/>
+      <c r="E165" s="4" t="inlineStr"/>
       <c r="F165" s="4" t="n">
         <v>37833</v>
       </c>
@@ -33572,16 +32364,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>25.49</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>+0.11</t>
-        </is>
-      </c>
+      <c r="D166" s="4" t="inlineStr"/>
+      <c r="E166" s="4" t="inlineStr"/>
       <c r="F166" s="4" t="n">
         <v>33690</v>
       </c>
@@ -33601,16 +32385,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>45.58</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
+      <c r="D167" s="4" t="inlineStr"/>
+      <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="n">
         <v>33231</v>
       </c>
@@ -33630,16 +32406,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>26.03</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>+0.04</t>
-        </is>
-      </c>
+      <c r="D168" s="4" t="inlineStr"/>
+      <c r="E168" s="4" t="inlineStr"/>
       <c r="F168" s="4" t="n">
         <v>19867</v>
       </c>
@@ -33659,16 +32427,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>28.13</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="D169" s="4" t="inlineStr"/>
+      <c r="E169" s="4" t="inlineStr"/>
       <c r="F169" s="4" t="n">
         <v>14357</v>
       </c>
@@ -33688,16 +32448,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>54.80</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="D170" s="4" t="inlineStr"/>
+      <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="n">
         <v>13039</v>
       </c>
@@ -33717,16 +32469,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>17.25</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
+      <c r="D171" s="4" t="inlineStr"/>
+      <c r="E171" s="4" t="inlineStr"/>
       <c r="F171" s="4" t="n">
         <v>11453</v>
       </c>
@@ -33746,11 +32490,7 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>9.55</t>
-        </is>
-      </c>
+      <c r="D172" s="4" t="inlineStr"/>
       <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="n">
         <v>8568</v>
@@ -33771,16 +32511,8 @@
           <t>統一台灣高息動能</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>18.04</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
+      <c r="D173" s="4" t="inlineStr"/>
+      <c r="E173" s="4" t="inlineStr"/>
       <c r="F173" s="4" t="n">
         <v>4429</v>
       </c>
@@ -33873,16 +32605,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>11.21</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="D179" s="4" t="inlineStr"/>
+      <c r="E179" s="4" t="inlineStr"/>
       <c r="F179" s="4" t="n">
         <v>-17439</v>
       </c>
@@ -33902,16 +32626,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>96.85</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="D180" s="4" t="inlineStr"/>
+      <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="n">
         <v>-15923</v>
       </c>
@@ -33931,16 +32647,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>118.05</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="D181" s="4" t="inlineStr"/>
+      <c r="E181" s="4" t="inlineStr"/>
       <c r="F181" s="4" t="n">
         <v>-3245</v>
       </c>
@@ -33960,16 +32668,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>8.97</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="D182" s="4" t="inlineStr"/>
+      <c r="E182" s="4" t="inlineStr"/>
       <c r="F182" s="4" t="n">
         <v>-1775</v>
       </c>
@@ -33989,16 +32689,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>32.52</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
+      <c r="D183" s="4" t="inlineStr"/>
+      <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="n">
         <v>-1325</v>
       </c>

--- a/StockInfo/tse_analysis_result.xlsx
+++ b/StockInfo/tse_analysis_result.xlsx
@@ -27253,16 +27253,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>25.89</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+0.34</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>96452</v>
       </c>
@@ -27286,16 +27278,8 @@
           <t xml:space="preserve">華邦電          </t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>134.00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+12.0</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>42375</v>
       </c>
@@ -27319,16 +27303,8 @@
           <t xml:space="preserve">大成鋼          </t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>39.80</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>34047</v>
       </c>
@@ -27352,16 +27328,8 @@
           <t xml:space="preserve">聯電            </t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>108.00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+9.6</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>33231</v>
       </c>
@@ -27385,16 +27353,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+0.39</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>24464</v>
       </c>
@@ -27418,16 +27378,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>26.10</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+0.43</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>24350</v>
       </c>
@@ -27451,11 +27403,7 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>11.17</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>23497</v>
@@ -27480,16 +27428,8 @@
           <t xml:space="preserve">燿華            </t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+3.8</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>20399</v>
       </c>
@@ -27513,16 +27453,8 @@
           <t xml:space="preserve">力積電          </t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>62.20</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>20169</v>
       </c>
@@ -27546,16 +27478,8 @@
           <t xml:space="preserve">華通            </t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>245.50</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>18832</v>
       </c>
@@ -27579,16 +27503,8 @@
           <t xml:space="preserve">彩晶            </t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>10.40</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>14097</v>
       </c>
@@ -27612,16 +27528,8 @@
           <t xml:space="preserve">敬鵬            </t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>53.90</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+2.6</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>13999</v>
       </c>
@@ -27645,16 +27553,8 @@
           <t xml:space="preserve">英業達          </t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>53.20</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>13348</v>
       </c>
@@ -27678,16 +27578,8 @@
           <t xml:space="preserve">台灣大          </t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>115.00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>13286</v>
       </c>
@@ -27711,16 +27603,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>55.55</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>11713</v>
       </c>
@@ -27744,11 +27628,7 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>10664</v>
@@ -27773,16 +27653,8 @@
           <t xml:space="preserve">華新科          </t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>220.00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+20.0</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>8640</v>
       </c>
@@ -27806,16 +27678,8 @@
           <t xml:space="preserve">益登            </t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>51.00</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+4.55</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>8578</v>
       </c>
@@ -27839,16 +27703,8 @@
           <t xml:space="preserve">新纖            </t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>17.25</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>8108</v>
       </c>
@@ -27872,16 +27728,8 @@
           <t xml:space="preserve">兆赫            </t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>70.70</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>7785</v>
       </c>
@@ -27905,16 +27753,8 @@
           <t xml:space="preserve">景碩            </t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>522.00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+24.5</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>7663</v>
       </c>
@@ -27938,16 +27778,8 @@
           <t xml:space="preserve">矽統            </t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>63.00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>7501</v>
       </c>
@@ -27971,16 +27803,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>28.12</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+0.17</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>7458</v>
       </c>
@@ -28004,16 +27828,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>31.96</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+0.11</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>7043</v>
       </c>
@@ -28037,16 +27853,8 @@
           <t xml:space="preserve">昇陽半導體      </t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>261.50</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+23.5</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>7014</v>
       </c>
@@ -28070,16 +27878,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>11.32</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+0.01</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>6994</v>
       </c>
@@ -28103,16 +27903,8 @@
           <t xml:space="preserve">晶豪科          </t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>238.00</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+21.5</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>6635</v>
       </c>
@@ -28136,16 +27928,8 @@
           <t xml:space="preserve">至上            </t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>84.50</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+2.3</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>6200</v>
       </c>
@@ -28169,16 +27953,8 @@
           <t xml:space="preserve">神基            </t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>103.50</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+5.6</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>5830</v>
       </c>
@@ -28202,16 +27978,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+0.07</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>5693</v>
       </c>
@@ -28235,16 +28003,8 @@
           <t xml:space="preserve">台虹            </t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>149.50</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+11.5</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>5566</v>
       </c>
@@ -28268,16 +28028,8 @@
           <t xml:space="preserve">華東            </t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>51.50</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+2.05</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>5374</v>
       </c>
@@ -28301,16 +28053,8 @@
           <t xml:space="preserve">台積電          </t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>2,270.00</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+50.0</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>5167</v>
       </c>
@@ -28334,16 +28078,8 @@
           <t xml:space="preserve">森崴能源        </t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>17.30</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>X0.0</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>4983</v>
       </c>
@@ -28367,16 +28103,8 @@
           <t>統一台灣高息動能</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>18.30</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+0.12</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>4882</v>
       </c>
@@ -28400,16 +28128,8 @@
           <t xml:space="preserve">南亞科          </t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>341.00</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+20.0</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>4804</v>
       </c>
@@ -28433,16 +28153,8 @@
           <t xml:space="preserve">威健            </t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>46.40</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+3.45</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>4424</v>
       </c>
@@ -28466,16 +28178,8 @@
           <t xml:space="preserve">富鼎            </t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>136.00</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>4415</v>
       </c>
@@ -28499,16 +28203,8 @@
           <t xml:space="preserve">今國光          </t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>68.30</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>4129</v>
       </c>
@@ -28532,16 +28228,8 @@
           <t xml:space="preserve">晶技            </t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>149.50</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>4102</v>
       </c>
@@ -28565,11 +28253,7 @@
           <t xml:space="preserve">第一金          </t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>29.50</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>3809</v>
@@ -28594,16 +28278,8 @@
           <t xml:space="preserve">智邦            </t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>2,675.00</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+240.0</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>3634</v>
       </c>
@@ -28627,16 +28303,8 @@
           <t xml:space="preserve">華泰            </t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>58.20</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>3439</v>
       </c>
@@ -28660,16 +28328,8 @@
           <t xml:space="preserve">富邦台50        </t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>222.50</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>3296</v>
       </c>
@@ -28693,11 +28353,7 @@
           <t xml:space="preserve">中華電          </t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>137.50</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>3132</v>
@@ -28722,16 +28378,8 @@
           <t xml:space="preserve">長榮            </t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>211.50</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>3100</v>
       </c>
@@ -28755,16 +28403,8 @@
           <t xml:space="preserve">聯詠            </t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>493.00</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>3056</v>
       </c>
@@ -28788,16 +28428,8 @@
           <t xml:space="preserve">華新            </t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>35.60</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>2894</v>
       </c>
@@ -28821,16 +28453,8 @@
           <t xml:space="preserve">正隆            </t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>2753</v>
       </c>
@@ -28854,16 +28478,8 @@
           <t xml:space="preserve">台表科          </t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>226.00</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+20.5</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>2709</v>
       </c>
@@ -28887,16 +28503,8 @@
           <t xml:space="preserve">興富發          </t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>43.15</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>2679</v>
       </c>
@@ -28920,16 +28528,8 @@
           <t xml:space="preserve">強茂            </t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>115.50</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>-5.5</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>2666</v>
       </c>
@@ -28953,16 +28553,8 @@
           <t xml:space="preserve">亞光            </t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>147.00</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>2579</v>
       </c>
@@ -28986,11 +28578,7 @@
           <t xml:space="preserve">上海商銀        </t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>40.30</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
       <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>2548</v>
@@ -29015,16 +28603,8 @@
           <t>國泰台灣科技龍頭</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>50.20</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>2456</v>
       </c>
@@ -29048,16 +28628,8 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>9.57</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+0.01</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>2398</v>
       </c>
@@ -29081,16 +28653,8 @@
           <t xml:space="preserve">創見            </t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>344.50</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+17.5</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>2385</v>
       </c>
@@ -29114,16 +28678,8 @@
           <t xml:space="preserve">增你強          </t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>78.80</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>2372</v>
       </c>
@@ -29147,16 +28703,8 @@
           <t xml:space="preserve">遠傳            </t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>98.10</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>2193</v>
       </c>
@@ -29180,16 +28728,8 @@
           <t xml:space="preserve">富邦金          </t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>94.60</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>2160</v>
       </c>
@@ -29213,16 +28753,8 @@
           <t xml:space="preserve">正文            </t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>39.15</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+1.15</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>2130</v>
       </c>
@@ -29246,16 +28778,8 @@
           <t xml:space="preserve">矽創            </t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>294.50</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+26.5</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>2117</v>
       </c>
@@ -29279,16 +28803,8 @@
           <t xml:space="preserve">台汽電          </t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>57.60</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>2116</v>
       </c>
@@ -29312,16 +28828,8 @@
           <t xml:space="preserve">亞翔            </t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>720.00</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+34.0</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>1974</v>
       </c>
@@ -29345,16 +28853,8 @@
           <t xml:space="preserve">達方            </t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>32.30</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+2.9</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>1953</v>
       </c>
@@ -29378,16 +28878,8 @@
           <t xml:space="preserve">中鼎            </t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>37.60</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>1950</v>
       </c>
@@ -29411,16 +28903,8 @@
           <t xml:space="preserve">中纖            </t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>6.68</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+0.17</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>1906</v>
       </c>
@@ -29444,16 +28928,8 @@
           <t xml:space="preserve">義隆            </t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>149.50</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>1836</v>
       </c>
@@ -29477,16 +28953,8 @@
           <t xml:space="preserve">和桐            </t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+0.11</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>1836</v>
       </c>
@@ -29510,16 +28978,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>36.25</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+0.13</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>1833</v>
       </c>
@@ -29543,16 +29003,8 @@
           <t xml:space="preserve">敦泰            </t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>57.80</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+2.1</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>1816</v>
       </c>
@@ -29576,16 +29028,8 @@
           <t xml:space="preserve">誠美材          </t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>1783</v>
       </c>
@@ -29609,16 +29053,8 @@
           <t xml:space="preserve">金像電          </t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>1,430.00</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+80.0</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>1730</v>
       </c>
@@ -29642,11 +29078,7 @@
           <t xml:space="preserve">凌華            </t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>111.50</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>1722</v>
@@ -29671,16 +29103,8 @@
           <t xml:space="preserve">台達化          </t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>16.10</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>1690</v>
       </c>
@@ -29704,16 +29128,8 @@
           <t xml:space="preserve">台亞            </t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>36.35</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>1675</v>
       </c>
@@ -29737,16 +29153,8 @@
           <t xml:space="preserve">材料*-KY        </t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>1600</v>
       </c>
@@ -29770,16 +29178,8 @@
           <t xml:space="preserve">矽力*-KY        </t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>503.00</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>+35.5</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>1487</v>
       </c>
@@ -29803,16 +29203,8 @@
           <t xml:space="preserve">技嘉            </t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>327.00</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+13.5</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>1464</v>
       </c>
@@ -29836,16 +29228,8 @@
           <t xml:space="preserve">佳能            </t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>80.30</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>1447</v>
       </c>
@@ -29869,16 +29253,8 @@
           <t xml:space="preserve">尖點            </t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>490.50</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+44.5</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>1396</v>
       </c>
@@ -29902,16 +29278,8 @@
           <t xml:space="preserve">凌陽            </t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>1391</v>
       </c>
@@ -29935,16 +29303,8 @@
           <t xml:space="preserve">台橡            </t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>1384</v>
       </c>
@@ -29968,16 +29328,8 @@
           <t xml:space="preserve">弘憶股          </t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>48.70</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+1.55</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>1372</v>
       </c>
@@ -30001,16 +29353,8 @@
           <t xml:space="preserve">宏達電          </t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>44.10</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>1344</v>
       </c>
@@ -30034,16 +29378,8 @@
           <t xml:space="preserve">京鼎            </t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>321.00</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>1258</v>
       </c>
@@ -30067,16 +29403,8 @@
           <t xml:space="preserve">麗正            </t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>1252</v>
       </c>
@@ -30100,16 +29428,8 @@
           <t xml:space="preserve">光寶科          </t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>207.00</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>1228</v>
       </c>
@@ -30133,16 +29453,8 @@
           <t xml:space="preserve">長榮航          </t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>1207</v>
       </c>
@@ -30166,16 +29478,8 @@
           <t xml:space="preserve">訊芯-KY         </t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>525.00</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+47.0</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>1198</v>
       </c>
@@ -30199,16 +29503,8 @@
           <t xml:space="preserve">同欣電          </t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>183.50</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>1193</v>
       </c>
@@ -30232,16 +29528,8 @@
           <t xml:space="preserve">信錦            </t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>97.80</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+5.8</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>1151</v>
       </c>
@@ -30265,16 +29553,8 @@
           <t xml:space="preserve">台郡            </t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>59.00</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>1117</v>
       </c>
@@ -30298,16 +29578,8 @@
           <t xml:space="preserve">大立光          </t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>3,135.00</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+285.0</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>1106</v>
       </c>
@@ -30331,16 +29603,8 @@
           <t xml:space="preserve">事欣科          </t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>66.90</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>1082</v>
       </c>
@@ -30364,16 +29628,8 @@
           <t xml:space="preserve">研華            </t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>465.00</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>1033</v>
       </c>
@@ -30397,16 +29653,8 @@
           <t xml:space="preserve">定穎投控        </t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>181.00</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>1025</v>
       </c>
@@ -30430,16 +29678,8 @@
           <t xml:space="preserve">中鴻            </t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>17.90</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>1007</v>
       </c>
@@ -30463,16 +29703,8 @@
           <t xml:space="preserve">統一            </t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>74.80</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>994</v>
       </c>
@@ -30496,16 +29728,8 @@
           <t xml:space="preserve">榮科            </t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>90.70</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>991</v>
       </c>
@@ -30606,16 +29830,8 @@
           <t xml:space="preserve">群創            </t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>35.40</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-204339</v>
       </c>
@@ -30639,16 +29855,8 @@
           <t xml:space="preserve">友達            </t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-26670</v>
       </c>
@@ -30672,16 +29880,8 @@
           <t xml:space="preserve">鴻海            </t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>244.50</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-6.5</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-23469</v>
       </c>
@@ -30705,16 +29905,8 @@
           <t xml:space="preserve">微星            </t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>117.00</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-20122</v>
       </c>
@@ -30738,16 +29930,8 @@
           <t xml:space="preserve">京元電子        </t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>296.00</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-9.0</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-18340</v>
       </c>
@@ -30771,16 +29955,8 @@
           <t xml:space="preserve">和碩            </t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>77.00</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-4.8</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-17883</v>
       </c>
@@ -30804,16 +29980,8 @@
           <t xml:space="preserve">彰銀            </t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>20.40</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-17324</v>
       </c>
@@ -30837,16 +30005,8 @@
           <t xml:space="preserve">仁寶            </t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>30.25</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-15531</v>
       </c>
@@ -30870,16 +30030,8 @@
           <t xml:space="preserve">台玻            </t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>66.90</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-15458</v>
       </c>
@@ -30903,16 +30055,8 @@
           <t xml:space="preserve">中鋼            </t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>18.30</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-15202</v>
       </c>
@@ -30936,16 +30080,8 @@
           <t xml:space="preserve">緯創            </t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>138.00</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-14456</v>
       </c>
@@ -30969,16 +30105,8 @@
           <t xml:space="preserve">台泥            </t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>24.55</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-14046</v>
       </c>
@@ -31002,16 +30130,8 @@
           <t xml:space="preserve">臺企銀          </t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>16.00</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-13526</v>
       </c>
@@ -31035,16 +30155,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>8.89</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-12561</v>
       </c>
@@ -31068,16 +30180,8 @@
           <t xml:space="preserve">華航            </t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>18.55</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-11356</v>
       </c>
@@ -31101,16 +30205,8 @@
           <t xml:space="preserve">台中銀          </t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-11227</v>
       </c>
@@ -31134,16 +30230,8 @@
           <t xml:space="preserve">金寶            </t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>28.25</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-10903</v>
       </c>
@@ -31167,16 +30255,8 @@
           <t xml:space="preserve">大同            </t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>29.00</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-10726</v>
       </c>
@@ -31200,16 +30280,8 @@
           <t xml:space="preserve">臻鼎-KY         </t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>436.50</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-10611</v>
       </c>
@@ -31233,16 +30305,8 @@
           <t xml:space="preserve">凱基金          </t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>22.10</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-10364</v>
       </c>
@@ -31266,16 +30330,8 @@
           <t xml:space="preserve">台新新光金      </t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>23.10</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-9111</v>
       </c>
@@ -31299,16 +30355,8 @@
           <t xml:space="preserve">合庫金          </t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-8844</v>
       </c>
@@ -31332,16 +30380,8 @@
           <t xml:space="preserve">元大金          </t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>55.50</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-8571</v>
       </c>
@@ -31365,16 +30405,8 @@
           <t xml:space="preserve">陽明            </t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>48.60</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-8534</v>
       </c>
@@ -31398,16 +30430,8 @@
           <t xml:space="preserve">台灣高鐵        </t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>25.90</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-8241</v>
       </c>
@@ -31431,16 +30455,8 @@
           <t xml:space="preserve">TPK-KY          </t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>64.30</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-2.3</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-8240</v>
       </c>
@@ -31464,16 +30480,8 @@
           <t xml:space="preserve">中工            </t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>12.90</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-7315</v>
       </c>
@@ -31497,16 +30505,8 @@
           <t xml:space="preserve">中環            </t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-7263</v>
       </c>
@@ -31530,11 +30530,7 @@
           <t xml:space="preserve">遠東新          </t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>26.75</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
       <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-7172</v>
@@ -31559,16 +30555,8 @@
           <t xml:space="preserve">長興            </t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>79.60</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-7013</v>
       </c>
@@ -31592,16 +30580,8 @@
           <t xml:space="preserve">玉山金          </t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-6710</v>
       </c>
@@ -31625,16 +30605,8 @@
           <t xml:space="preserve">南亞            </t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>85.30</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-6488</v>
       </c>
@@ -31658,16 +30630,8 @@
           <t xml:space="preserve">富采            </t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>68.20</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-6124</v>
       </c>
@@ -31691,16 +30655,8 @@
           <t xml:space="preserve">億光            </t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>65.70</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-7.2</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-5711</v>
       </c>
@@ -31724,16 +30680,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>96.05</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-5468</v>
       </c>
@@ -31757,16 +30705,8 @@
           <t xml:space="preserve">映泰            </t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>47.20</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-5362</v>
       </c>
@@ -31790,16 +30730,8 @@
           <t xml:space="preserve">元晶            </t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>39.80</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-2.35</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-5361</v>
       </c>
@@ -31823,16 +30755,8 @@
           <t xml:space="preserve">南電            </t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>847.00</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-33.0</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-5304</v>
       </c>
@@ -31856,16 +30780,8 @@
           <t xml:space="preserve">台化            </t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>44.95</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-4805</v>
       </c>
@@ -31889,16 +30805,8 @@
           <t xml:space="preserve">宏碁            </t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>28.00</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-4646</v>
       </c>
@@ -31922,16 +30830,8 @@
           <t xml:space="preserve">統一證          </t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-4558</v>
       </c>
@@ -31955,16 +30855,8 @@
           <t xml:space="preserve">文曄            </t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>271.50</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>-12.5</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-4416</v>
       </c>
@@ -31988,16 +30880,8 @@
           <t xml:space="preserve">寶成            </t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-4406</v>
       </c>
@@ -32021,16 +30905,8 @@
           <t xml:space="preserve">台塑            </t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>46.10</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-4357</v>
       </c>
@@ -32054,16 +30930,8 @@
           <t xml:space="preserve">兆豐金          </t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>39.30</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-4334</v>
       </c>
@@ -32087,16 +30955,8 @@
           <t xml:space="preserve">可成            </t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>190.50</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-12.0</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-4295</v>
       </c>
@@ -32120,16 +30980,8 @@
           <t xml:space="preserve">國泰金          </t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>76.70</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-4170</v>
       </c>
@@ -32153,16 +31005,8 @@
           <t xml:space="preserve">遠東銀          </t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>12.05</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-3984</v>
       </c>
@@ -32186,16 +31030,8 @@
           <t xml:space="preserve">中磊            </t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>77.70</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>-1.7</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-3687</v>
       </c>
@@ -32219,16 +31055,8 @@
           <t xml:space="preserve">聯合再生        </t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>17.70</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-3621</v>
       </c>
@@ -32320,16 +31148,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>25.89</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>+0.34</t>
-        </is>
-      </c>
+      <c r="D164" s="4" t="inlineStr"/>
+      <c r="E164" s="4" t="inlineStr"/>
       <c r="F164" s="4" t="n">
         <v>96452</v>
       </c>
@@ -32349,16 +31169,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>25.87</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>+0.39</t>
-        </is>
-      </c>
+      <c r="D165" s="4" t="inlineStr"/>
+      <c r="E165" s="4" t="inlineStr"/>
       <c r="F165" s="4" t="n">
         <v>24464</v>
       </c>
@@ -32378,16 +31190,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>26.10</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>+0.43</t>
-        </is>
-      </c>
+      <c r="D166" s="4" t="inlineStr"/>
+      <c r="E166" s="4" t="inlineStr"/>
       <c r="F166" s="4" t="n">
         <v>24350</v>
       </c>
@@ -32407,11 +31211,7 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>11.17</t>
-        </is>
-      </c>
+      <c r="D167" s="4" t="inlineStr"/>
       <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="n">
         <v>23497</v>
@@ -32432,16 +31232,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>55.55</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="D168" s="4" t="inlineStr"/>
+      <c r="E168" s="4" t="inlineStr"/>
       <c r="F168" s="4" t="n">
         <v>11713</v>
       </c>
@@ -32461,11 +31253,7 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
+      <c r="D169" s="4" t="inlineStr"/>
       <c r="E169" s="4" t="inlineStr"/>
       <c r="F169" s="4" t="n">
         <v>10664</v>
@@ -32486,16 +31274,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>28.12</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>+0.17</t>
-        </is>
-      </c>
+      <c r="D170" s="4" t="inlineStr"/>
+      <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="n">
         <v>7458</v>
       </c>
@@ -32515,16 +31295,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>31.96</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>+0.11</t>
-        </is>
-      </c>
+      <c r="D171" s="4" t="inlineStr"/>
+      <c r="E171" s="4" t="inlineStr"/>
       <c r="F171" s="4" t="n">
         <v>7043</v>
       </c>
@@ -32544,16 +31316,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>11.32</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>+0.01</t>
-        </is>
-      </c>
+      <c r="D172" s="4" t="inlineStr"/>
+      <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="n">
         <v>6994</v>
       </c>
@@ -32573,16 +31337,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>+0.07</t>
-        </is>
-      </c>
+      <c r="D173" s="4" t="inlineStr"/>
+      <c r="E173" s="4" t="inlineStr"/>
       <c r="F173" s="4" t="n">
         <v>5693</v>
       </c>
@@ -32675,16 +31431,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>8.89</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="D179" s="4" t="inlineStr"/>
+      <c r="E179" s="4" t="inlineStr"/>
       <c r="F179" s="4" t="n">
         <v>-12561</v>
       </c>
@@ -32704,16 +31452,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>96.05</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="D180" s="4" t="inlineStr"/>
+      <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="n">
         <v>-5468</v>
       </c>
@@ -32733,16 +31473,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>119.45</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="D181" s="4" t="inlineStr"/>
+      <c r="E181" s="4" t="inlineStr"/>
       <c r="F181" s="4" t="n">
         <v>-3306</v>
       </c>
@@ -32762,16 +31494,8 @@
           <t xml:space="preserve">中信中國高股息  </t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>16.27</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
+      <c r="D182" s="4" t="inlineStr"/>
+      <c r="E182" s="4" t="inlineStr"/>
       <c r="F182" s="4" t="n">
         <v>-1320</v>
       </c>
@@ -32791,16 +31515,8 @@
           <t xml:space="preserve">元大S&amp;P500      </t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>73.85</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="D183" s="4" t="inlineStr"/>
+      <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="n">
         <v>-949</v>
       </c>

--- a/StockInfo/tse_analysis_result.xlsx
+++ b/StockInfo/tse_analysis_result.xlsx
@@ -28729,16 +28729,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>30.81</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+0.46</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>102539</v>
       </c>
@@ -28762,16 +28754,8 @@
           <t xml:space="preserve">友達            </t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>56969</v>
       </c>
@@ -28795,16 +28779,8 @@
           <t xml:space="preserve">永豐金          </t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>39.80</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+3.45</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>45822</v>
       </c>
@@ -28828,16 +28804,8 @@
           <t xml:space="preserve">台塑            </t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>51.70</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+3.75</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>35302</v>
       </c>
@@ -28861,16 +28829,8 @@
           <t xml:space="preserve">中鋼            </t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>19.10</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>34629</v>
       </c>
@@ -28894,16 +28854,8 @@
           <t xml:space="preserve">旺宏            </t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>169.00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+7.5</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>31273</v>
       </c>
@@ -28927,16 +28879,8 @@
           <t xml:space="preserve">台玻            </t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>71.30</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>28388</v>
       </c>
@@ -28960,16 +28904,8 @@
           <t xml:space="preserve">聯電            </t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>145.50</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>24814</v>
       </c>
@@ -28993,16 +28929,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>31.10</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+0.53</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>20821</v>
       </c>
@@ -29026,16 +28954,8 @@
           <t xml:space="preserve">華航            </t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>19425</v>
       </c>
@@ -29059,16 +28979,8 @@
           <t xml:space="preserve">力積電          </t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>74.20</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>18607</v>
       </c>
@@ -29092,16 +29004,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>12.70</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+0.17</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>18182</v>
       </c>
@@ -29125,16 +29029,8 @@
           <t xml:space="preserve">京元電子        </t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>308.50</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+28.0</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>17708</v>
       </c>
@@ -29158,16 +29054,8 @@
           <t xml:space="preserve">南茂            </t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>104.00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+9.1</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>17268</v>
       </c>
@@ -29191,16 +29079,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>32.00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>X0.0</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>16675</v>
       </c>
@@ -29224,16 +29104,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>107.30</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>15692</v>
       </c>
@@ -29257,16 +29129,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>38.33</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+0.82</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>14088</v>
       </c>
@@ -29290,16 +29154,8 @@
           <t xml:space="preserve">鼎元            </t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>81.80</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+7.4</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>12519</v>
       </c>
@@ -29323,16 +29179,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>12459</v>
       </c>
@@ -29356,16 +29204,8 @@
           <t xml:space="preserve">第一金          </t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>32.60</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>11556</v>
       </c>
@@ -29389,16 +29229,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>52.80</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>10680</v>
       </c>
@@ -29422,16 +29254,8 @@
           <t xml:space="preserve">中環            </t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>11.75</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>9260</v>
       </c>
@@ -29455,11 +29279,7 @@
           <t xml:space="preserve">合庫金          </t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>24.75</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>8826</v>
@@ -29484,16 +29304,8 @@
           <t xml:space="preserve">中石化          </t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>7.78</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+0.16</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>8656</v>
       </c>
@@ -29517,16 +29329,8 @@
           <t xml:space="preserve">中信金          </t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>71.90</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>8435</v>
       </c>
@@ -29550,16 +29354,8 @@
           <t xml:space="preserve">南亞科          </t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>459.50</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+22.5</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>8338</v>
       </c>
@@ -29583,16 +29379,8 @@
           <t xml:space="preserve">東鹼            </t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>50.30</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+4.55</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>8246</v>
       </c>
@@ -29616,16 +29404,8 @@
           <t xml:space="preserve">威盛            </t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>81.40</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>7938</v>
       </c>
@@ -29649,16 +29429,8 @@
           <t xml:space="preserve">凌陽            </t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>7890</v>
       </c>
@@ -29682,11 +29454,7 @@
           <t xml:space="preserve">長榮航          </t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>7178</v>
@@ -29711,16 +29479,8 @@
           <t xml:space="preserve">遠東新          </t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>6835</v>
       </c>
@@ -29744,16 +29504,8 @@
           <t xml:space="preserve">裕民            </t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>61.50</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>6827</v>
       </c>
@@ -29777,16 +29529,8 @@
           <t xml:space="preserve">三商壽          </t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>8.74</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+0.12</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>5902</v>
       </c>
@@ -29810,16 +29554,8 @@
           <t xml:space="preserve">日月光投控      </t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>613.00</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+18.0</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>5896</v>
       </c>
@@ -29843,16 +29579,8 @@
           <t xml:space="preserve">聯茂            </t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>280.00</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>5262</v>
       </c>
@@ -29876,16 +29604,8 @@
           <t xml:space="preserve">華南金          </t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>38.35</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>4960</v>
       </c>
@@ -29909,16 +29629,8 @@
           <t xml:space="preserve">台亞            </t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>39.95</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+1.45</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>4906</v>
       </c>
@@ -29942,16 +29654,8 @@
           <t xml:space="preserve">菱生            </t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>36.85</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+2.35</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>4833</v>
       </c>
@@ -29975,16 +29679,8 @@
           <t xml:space="preserve">南亞            </t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>139.00</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>4682</v>
       </c>
@@ -30008,16 +29704,8 @@
           <t xml:space="preserve">華紙            </t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>17.10</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+1.55</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>4402</v>
       </c>
@@ -30041,16 +29729,8 @@
           <t xml:space="preserve">凌巨            </t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>21.90</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>4167</v>
       </c>
@@ -30074,16 +29754,8 @@
           <t xml:space="preserve">聯鈞            </t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>565.00</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+51.0</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>4106</v>
       </c>
@@ -30107,16 +29779,8 @@
           <t xml:space="preserve">矽格            </t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>235.00</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>+21.0</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>4087</v>
       </c>
@@ -30140,16 +29804,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+0.11</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>3905</v>
       </c>
@@ -30173,16 +29829,8 @@
           <t xml:space="preserve">大聯大          </t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>112.00</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>3210</v>
       </c>
@@ -30206,16 +29854,8 @@
           <t xml:space="preserve">鈞寶            </t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>98.50</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+8.9</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>3205</v>
       </c>
@@ -30239,16 +29879,8 @@
           <t xml:space="preserve">晶豪科          </t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>237.50</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>3139</v>
       </c>
@@ -30272,16 +29904,8 @@
           <t xml:space="preserve">智原            </t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>209.00</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>2965</v>
       </c>
@@ -30305,16 +29929,8 @@
           <t xml:space="preserve">華泰            </t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>55.60</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>2891</v>
       </c>
@@ -30338,16 +29954,8 @@
           <t xml:space="preserve">廣達            </t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>376.00</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>2799</v>
       </c>
@@ -30371,16 +29979,8 @@
           <t xml:space="preserve">至上            </t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>98.20</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>2669</v>
       </c>
@@ -30404,16 +30004,8 @@
           <t xml:space="preserve">台化            </t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>54.20</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>2620</v>
       </c>
@@ -30437,16 +30029,8 @@
           <t xml:space="preserve">矽統            </t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>62.90</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+3.9</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>2579</v>
       </c>
@@ -30470,16 +30054,8 @@
           <t xml:space="preserve">艾姆勒          </t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>50.60</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+4.55</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>2561</v>
       </c>
@@ -30503,16 +30079,8 @@
           <t xml:space="preserve">超豐            </t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>135.00</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>2523</v>
       </c>
@@ -30536,16 +30104,8 @@
           <t xml:space="preserve">兆豐金          </t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>45.50</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>2503</v>
       </c>
@@ -30569,16 +30129,8 @@
           <t xml:space="preserve">台聚            </t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>13.55</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>2484</v>
       </c>
@@ -30602,16 +30154,8 @@
           <t xml:space="preserve">益登            </t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>73.50</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>2478</v>
       </c>
@@ -30635,16 +30179,8 @@
           <t xml:space="preserve">銘異            </t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>37.90</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>2447</v>
       </c>
@@ -30668,16 +30204,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>41.22</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>+0.61</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>2371</v>
       </c>
@@ -30701,16 +30229,8 @@
           <t xml:space="preserve">台塑化          </t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>53.50</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>2332</v>
       </c>
@@ -30734,16 +30254,8 @@
           <t xml:space="preserve">中興電          </t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>176.50</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>2304</v>
       </c>
@@ -30767,16 +30279,8 @@
           <t xml:space="preserve">富采            </t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>67.20</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>2249</v>
       </c>
@@ -30800,16 +30304,8 @@
           <t xml:space="preserve">定穎投控        </t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>179.00</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>2236</v>
       </c>
@@ -30833,16 +30329,8 @@
           <t xml:space="preserve">集盛            </t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>10.20</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+0.38</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>2175</v>
       </c>
@@ -30866,16 +30354,8 @@
           <t xml:space="preserve">聯成            </t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>11.60</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>2170</v>
       </c>
@@ -30899,16 +30379,8 @@
           <t xml:space="preserve">榮成            </t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>10.20</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>2119</v>
       </c>
@@ -30932,16 +30404,8 @@
           <t xml:space="preserve">義隆            </t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>172.00</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+15.5</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>2118</v>
       </c>
@@ -30965,16 +30429,8 @@
           <t xml:space="preserve">嘉聯益          </t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>2061</v>
       </c>
@@ -30998,16 +30454,8 @@
           <t xml:space="preserve">宏致            </t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>80.50</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>+3.4</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>2048</v>
       </c>
@@ -31031,16 +30479,8 @@
           <t xml:space="preserve">騰輝電子-KY     </t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>245.50</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+19.0</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>2037</v>
       </c>
@@ -31064,16 +30504,8 @@
           <t xml:space="preserve">台橡            </t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>21.40</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>1995</v>
       </c>
@@ -31097,16 +30529,8 @@
           <t xml:space="preserve">永豐餘          </t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>28.20</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>1920</v>
       </c>
@@ -31130,16 +30554,8 @@
           <t xml:space="preserve">威健            </t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>49.50</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>1790</v>
       </c>
@@ -31163,16 +30579,8 @@
           <t xml:space="preserve">偉詮電          </t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>73.40</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>1738</v>
       </c>
@@ -31196,16 +30604,8 @@
           <t xml:space="preserve">王道銀行        </t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>10.50</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>1695</v>
       </c>
@@ -31229,16 +30629,8 @@
           <t xml:space="preserve">微星            </t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>138.50</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>1670</v>
       </c>
@@ -31262,16 +30654,8 @@
           <t xml:space="preserve">立隆電          </t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>402.00</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>+36.5</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>1646</v>
       </c>
@@ -31295,16 +30679,8 @@
           <t xml:space="preserve">臻鼎-KY         </t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>642.00</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>1643</v>
       </c>
@@ -31328,16 +30704,8 @@
           <t xml:space="preserve">同欣電          </t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>242.50</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+17.5</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>1628</v>
       </c>
@@ -31361,16 +30729,8 @@
           <t xml:space="preserve">瑞昱            </t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>819.00</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+74.0</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>1575</v>
       </c>
@@ -31394,16 +30754,8 @@
           <t xml:space="preserve">中纖            </t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>9.86</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+0.07</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>1515</v>
       </c>
@@ -31427,16 +30779,8 @@
           <t xml:space="preserve">錸德            </t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>13.85</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>1511</v>
       </c>
@@ -31460,16 +30804,8 @@
           <t xml:space="preserve">彰銀            </t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>1490</v>
       </c>
@@ -31493,16 +30829,8 @@
           <t>國泰台灣科技龍頭</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>55.40</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>1475</v>
       </c>
@@ -31526,16 +30854,8 @@
           <t xml:space="preserve">群益證          </t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>39.65</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>1460</v>
       </c>
@@ -31559,16 +30879,8 @@
           <t xml:space="preserve">宏齊            </t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>28.30</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>1400</v>
       </c>
@@ -31592,16 +30904,8 @@
           <t xml:space="preserve">國建            </t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>26.85</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>1394</v>
       </c>
@@ -31625,16 +30929,8 @@
           <t xml:space="preserve">亞光            </t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>160.50</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>1364</v>
       </c>
@@ -31658,16 +30954,8 @@
           <t xml:space="preserve">光罩            </t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>53.30</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>1356</v>
       </c>
@@ -31691,16 +30979,8 @@
           <t xml:space="preserve">力智            </t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>260.50</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+23.5</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>1322</v>
       </c>
@@ -31724,16 +31004,8 @@
           <t xml:space="preserve">和碩            </t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>82.90</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>1318</v>
       </c>
@@ -31757,16 +31029,8 @@
           <t xml:space="preserve">亞泥            </t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>35.80</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>1298</v>
       </c>
@@ -31790,16 +31054,8 @@
           <t xml:space="preserve">新唐            </t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>196.50</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+9.0</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>1297</v>
       </c>
@@ -31823,16 +31079,8 @@
           <t xml:space="preserve">一詮            </t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>276.50</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+25.0</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>1289</v>
       </c>
@@ -31856,16 +31104,8 @@
           <t xml:space="preserve">日電貿          </t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>332.50</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+30.0</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>1270</v>
       </c>
@@ -31889,16 +31129,8 @@
           <t xml:space="preserve">金寶            </t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>35.50</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>1229</v>
       </c>
@@ -31922,16 +31154,8 @@
           <t xml:space="preserve">富邦台50        </t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>249.10</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>1226</v>
       </c>
@@ -31955,16 +31179,8 @@
           <t xml:space="preserve">達運            </t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>15.05</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>1198</v>
       </c>
@@ -31988,16 +31204,8 @@
           <t xml:space="preserve">百容            </t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>39.65</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+3.6</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>1184</v>
       </c>
@@ -32098,16 +31306,8 @@
           <t xml:space="preserve">彩晶            </t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>18.80</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-80501</v>
       </c>
@@ -32131,16 +31331,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>8.60</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-49733</v>
       </c>
@@ -32164,16 +31356,8 @@
           <t xml:space="preserve">鴻海            </t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>268.50</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-29377</v>
       </c>
@@ -32197,16 +31381,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>10.03</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-24020</v>
       </c>
@@ -32230,16 +31406,8 @@
           <t xml:space="preserve">聯合再生        </t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-21397</v>
       </c>
@@ -32263,16 +31431,8 @@
           <t xml:space="preserve">緯創            </t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>161.50</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-20744</v>
       </c>
@@ -32296,16 +31456,8 @@
           <t xml:space="preserve">寶成            </t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-17485</v>
       </c>
@@ -32329,16 +31481,8 @@
           <t xml:space="preserve">新纖            </t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>25.60</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-2.35</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-14935</v>
       </c>
@@ -32362,16 +31506,8 @@
           <t xml:space="preserve">中信中國高股息  </t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-14066</v>
       </c>
@@ -32395,16 +31531,8 @@
           <t xml:space="preserve">華新            </t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-12105</v>
       </c>
@@ -32428,16 +31556,8 @@
           <t xml:space="preserve">華邦電          </t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>218.50</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>+19.5</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-11026</v>
       </c>
@@ -32461,16 +31581,8 @@
           <t xml:space="preserve">臺企銀          </t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-10431</v>
       </c>
@@ -32494,16 +31606,8 @@
           <t xml:space="preserve">台泥            </t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>24.50</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-9189</v>
       </c>
@@ -32527,16 +31631,8 @@
           <t xml:space="preserve">華新科          </t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>561.00</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>+19.0</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-8495</v>
       </c>
@@ -32560,16 +31656,8 @@
           <t xml:space="preserve">玉山金          </t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>35.40</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-8223</v>
       </c>
@@ -32593,16 +31681,8 @@
           <t xml:space="preserve">群創            </t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>64.40</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>+5.8</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-7778</v>
       </c>
@@ -32626,16 +31706,8 @@
           <t xml:space="preserve">新興            </t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>31.00</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-7759</v>
       </c>
@@ -32659,16 +31731,8 @@
           <t xml:space="preserve">華通            </t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>259.50</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-7269</v>
       </c>
@@ -32692,16 +31756,8 @@
           <t xml:space="preserve">國泰金          </t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>115.50</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-6541</v>
       </c>
@@ -32725,16 +31781,8 @@
           <t xml:space="preserve">映泰            </t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-3.85</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-6200</v>
       </c>
@@ -32758,16 +31806,8 @@
           <t xml:space="preserve">仁寶            </t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>37.75</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-5993</v>
       </c>
@@ -32791,16 +31831,8 @@
           <t xml:space="preserve">TPK-KY          </t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>86.20</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-5929</v>
       </c>
@@ -32824,16 +31856,8 @@
           <t xml:space="preserve">弘憶股          </t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>62.80</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-5389</v>
       </c>
@@ -32857,16 +31881,8 @@
           <t xml:space="preserve">和桐            </t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-5308</v>
       </c>
@@ -32890,16 +31906,8 @@
           <t xml:space="preserve">凱基金          </t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-5305</v>
       </c>
@@ -32923,16 +31931,8 @@
           <t xml:space="preserve">遠東銀          </t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>12.95</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-4985</v>
       </c>
@@ -32956,16 +31956,8 @@
           <t xml:space="preserve">國碩            </t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>34.85</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-4941</v>
       </c>
@@ -32989,16 +31981,8 @@
           <t xml:space="preserve">英業達          </t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>67.70</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-4906</v>
       </c>
@@ -33022,16 +32006,8 @@
           <t xml:space="preserve">華晶科          </t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-4504</v>
       </c>
@@ -33055,16 +32031,8 @@
           <t xml:space="preserve">陽明            </t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>51.30</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-4396</v>
       </c>
@@ -33088,16 +32056,8 @@
           <t xml:space="preserve">欣興            </t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>968.00</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-20.0</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-4077</v>
       </c>
@@ -33121,16 +32081,8 @@
           <t xml:space="preserve">文曄            </t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>222.50</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-3956</v>
       </c>
@@ -33154,16 +32106,8 @@
           <t xml:space="preserve">可寧衛*         </t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>28.10</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-3846</v>
       </c>
@@ -33187,16 +32131,8 @@
           <t xml:space="preserve">瑞軒            </t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>48.15</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-3682</v>
       </c>
@@ -33220,16 +32156,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>61.70</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-3663</v>
       </c>
@@ -33253,16 +32181,8 @@
           <t xml:space="preserve">統一            </t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>74.50</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-3633</v>
       </c>
@@ -33286,16 +32206,8 @@
           <t xml:space="preserve">大成鋼          </t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>41.00</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-3558</v>
       </c>
@@ -33319,16 +32231,8 @@
           <t xml:space="preserve">宏碁            </t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>34.40</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-3409</v>
       </c>
@@ -33352,16 +32256,8 @@
           <t xml:space="preserve">大毅            </t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>234.00</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-3104</v>
       </c>
@@ -33385,16 +32281,8 @@
           <t xml:space="preserve">普安            </t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>52.10</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-1.7</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-3060</v>
       </c>
@@ -33418,16 +32306,8 @@
           <t xml:space="preserve">統一超          </t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>223.50</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>-5.5</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-3028</v>
       </c>
@@ -33451,16 +32331,8 @@
           <t xml:space="preserve">台新新光金      </t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>32.45</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-2709</v>
       </c>
@@ -33484,16 +32356,8 @@
           <t xml:space="preserve">華碩            </t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>789.00</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>-14.0</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-2689</v>
       </c>
@@ -33517,11 +32381,7 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>9.61</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
       <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-2640</v>
@@ -33546,16 +32406,8 @@
           <t xml:space="preserve">創見            </t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>311.50</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-2601</v>
       </c>
@@ -33579,16 +32431,8 @@
           <t xml:space="preserve">富邦金          </t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>138.00</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-2595</v>
       </c>
@@ -33612,16 +32456,8 @@
           <t xml:space="preserve">致伸            </t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>75.90</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-2587</v>
       </c>
@@ -33645,16 +32481,8 @@
           <t xml:space="preserve">可成            </t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>202.50</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-2438</v>
       </c>
@@ -33678,16 +32506,8 @@
           <t xml:space="preserve">景碩            </t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>724.00</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>+18.0</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-2416</v>
       </c>
@@ -33711,16 +32531,8 @@
           <t xml:space="preserve">東陽            </t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>99.20</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-3.3</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-2317</v>
       </c>
@@ -33812,16 +32624,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>30.81</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>+0.46</t>
-        </is>
-      </c>
+      <c r="D164" s="4" t="inlineStr"/>
+      <c r="E164" s="4" t="inlineStr"/>
       <c r="F164" s="4" t="n">
         <v>102539</v>
       </c>
@@ -33841,16 +32645,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>31.10</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>+0.53</t>
-        </is>
-      </c>
+      <c r="D165" s="4" t="inlineStr"/>
+      <c r="E165" s="4" t="inlineStr"/>
       <c r="F165" s="4" t="n">
         <v>20821</v>
       </c>
@@ -33870,16 +32666,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>12.70</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>+0.17</t>
-        </is>
-      </c>
+      <c r="D166" s="4" t="inlineStr"/>
+      <c r="E166" s="4" t="inlineStr"/>
       <c r="F166" s="4" t="n">
         <v>18182</v>
       </c>
@@ -33899,16 +32687,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>32.00</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>X0.0</t>
-        </is>
-      </c>
+      <c r="D167" s="4" t="inlineStr"/>
+      <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="n">
         <v>16675</v>
       </c>
@@ -33928,16 +32708,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>107.30</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="D168" s="4" t="inlineStr"/>
+      <c r="E168" s="4" t="inlineStr"/>
       <c r="F168" s="4" t="n">
         <v>15692</v>
       </c>
@@ -33957,16 +32729,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>38.33</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>+0.82</t>
-        </is>
-      </c>
+      <c r="D169" s="4" t="inlineStr"/>
+      <c r="E169" s="4" t="inlineStr"/>
       <c r="F169" s="4" t="n">
         <v>14088</v>
       </c>
@@ -33986,16 +32750,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="D170" s="4" t="inlineStr"/>
+      <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="n">
         <v>12459</v>
       </c>
@@ -34015,16 +32771,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>52.80</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="D171" s="4" t="inlineStr"/>
+      <c r="E171" s="4" t="inlineStr"/>
       <c r="F171" s="4" t="n">
         <v>10680</v>
       </c>
@@ -34044,16 +32792,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>+0.11</t>
-        </is>
-      </c>
+      <c r="D172" s="4" t="inlineStr"/>
+      <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="n">
         <v>3905</v>
       </c>
@@ -34073,16 +32813,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>41.22</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>+0.61</t>
-        </is>
-      </c>
+      <c r="D173" s="4" t="inlineStr"/>
+      <c r="E173" s="4" t="inlineStr"/>
       <c r="F173" s="4" t="n">
         <v>2371</v>
       </c>
@@ -34175,16 +32907,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>8.60</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
+      <c r="D179" s="4" t="inlineStr"/>
+      <c r="E179" s="4" t="inlineStr"/>
       <c r="F179" s="4" t="n">
         <v>-49733</v>
       </c>
@@ -34204,16 +32928,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>10.03</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
+      <c r="D180" s="4" t="inlineStr"/>
+      <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="n">
         <v>-24020</v>
       </c>
@@ -34233,16 +32949,8 @@
           <t xml:space="preserve">中信中國高股息  </t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="D181" s="4" t="inlineStr"/>
+      <c r="E181" s="4" t="inlineStr"/>
       <c r="F181" s="4" t="n">
         <v>-14066</v>
       </c>
@@ -34262,16 +32970,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>61.70</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="D182" s="4" t="inlineStr"/>
+      <c r="E182" s="4" t="inlineStr"/>
       <c r="F182" s="4" t="n">
         <v>-3663</v>
       </c>
@@ -34291,11 +32991,7 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>9.61</t>
-        </is>
-      </c>
+      <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="n">
         <v>-2640</v>
@@ -34316,16 +33012,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>121.80</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="D184" s="4" t="inlineStr"/>
+      <c r="E184" s="4" t="inlineStr"/>
       <c r="F184" s="4" t="n">
         <v>-1973</v>
       </c>
@@ -34345,16 +33033,8 @@
           <t xml:space="preserve">元大S&amp;P500      </t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>74.25</t>
-        </is>
-      </c>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="D185" s="4" t="inlineStr"/>
+      <c r="E185" s="4" t="inlineStr"/>
       <c r="F185" s="4" t="n">
         <v>-1478</v>
       </c>

--- a/StockInfo/tse_analysis_result.xlsx
+++ b/StockInfo/tse_analysis_result.xlsx
@@ -28537,16 +28537,8 @@
           <t xml:space="preserve">力積電          </t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>85.70</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+7.1</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>88899</v>
       </c>
@@ -28570,16 +28562,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>10.04</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+0.22</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>82225</v>
       </c>
@@ -28603,16 +28587,8 @@
           <t xml:space="preserve">華航            </t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>69053</v>
       </c>
@@ -28636,16 +28612,8 @@
           <t xml:space="preserve">長榮航          </t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>44.00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>27233</v>
       </c>
@@ -28669,16 +28637,8 @@
           <t xml:space="preserve">台塑            </t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>54.50</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+4.95</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>21809</v>
       </c>
@@ -28702,16 +28662,8 @@
           <t xml:space="preserve">台化            </t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>57.70</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>X0.0</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>21471</v>
       </c>
@@ -28735,16 +28687,8 @@
           <t xml:space="preserve">臺企銀          </t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>17.80</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>15228</v>
       </c>
@@ -28768,16 +28712,8 @@
           <t xml:space="preserve">中鋼            </t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>14083</v>
       </c>
@@ -28801,16 +28737,8 @@
           <t xml:space="preserve">凌巨            </t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>23.50</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+2.1</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>10207</v>
       </c>
@@ -28834,16 +28762,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>8.60</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+0.07</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>10122</v>
       </c>
@@ -28867,16 +28787,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>32.08</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+0.08</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>9420</v>
       </c>
@@ -28900,16 +28812,8 @@
           <t xml:space="preserve">和碩            </t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>84.00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+3.6</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>6730</v>
       </c>
@@ -28933,16 +28837,8 @@
           <t xml:space="preserve">中石化          </t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>7.99</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+0.14</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>6206</v>
       </c>
@@ -28966,16 +28862,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>12.66</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>6132</v>
       </c>
@@ -28999,16 +28887,8 @@
           <t xml:space="preserve">興富發          </t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>43.10</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>5265</v>
       </c>
@@ -29032,16 +28912,8 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>9.64</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+0.01</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>4744</v>
       </c>
@@ -29065,16 +28937,8 @@
           <t xml:space="preserve">第一金          </t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>32.05</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>4391</v>
       </c>
@@ -29098,16 +28962,8 @@
           <t xml:space="preserve">南電            </t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>955.00</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+46.0</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>4173</v>
       </c>
@@ -29131,16 +28987,8 @@
           <t xml:space="preserve">聯茂            </t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>309.00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+28.0</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>3944</v>
       </c>
@@ -29164,16 +29012,8 @@
           <t xml:space="preserve">映泰            </t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>54.30</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+3.4</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>3780</v>
       </c>
@@ -29197,16 +29037,8 @@
           <t xml:space="preserve">菱生            </t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>43.30</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>3772</v>
       </c>
@@ -29230,16 +29062,8 @@
           <t xml:space="preserve">台聚            </t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>13.60</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>3762</v>
       </c>
@@ -29263,16 +29087,8 @@
           <t xml:space="preserve">和桐            </t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>19.05</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>3642</v>
       </c>
@@ -29296,16 +29112,8 @@
           <t xml:space="preserve">台灣大          </t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>119.50</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>3617</v>
       </c>
@@ -29329,16 +29137,8 @@
           <t xml:space="preserve">英業達          </t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>66.40</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>3485</v>
       </c>
@@ -29362,16 +29162,8 @@
           <t xml:space="preserve">凌陽            </t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>34.80</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>3419</v>
       </c>
@@ -29395,16 +29187,8 @@
           <t xml:space="preserve">台塑化          </t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>55.20</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+3.1</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>3381</v>
       </c>
@@ -29428,16 +29212,8 @@
           <t xml:space="preserve">遠東新          </t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>3347</v>
       </c>
@@ -29461,16 +29237,8 @@
           <t xml:space="preserve">宏碁            </t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>34.20</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>3243</v>
       </c>
@@ -29494,16 +29262,8 @@
           <t xml:space="preserve">合庫金          </t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>24.40</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>3125</v>
       </c>
@@ -29527,16 +29287,8 @@
           <t xml:space="preserve">聯傑            </t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>45.25</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+4.1</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>3108</v>
       </c>
@@ -29560,16 +29312,8 @@
           <t xml:space="preserve">長興            </t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>73.90</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>3101</v>
       </c>
@@ -29593,16 +29337,8 @@
           <t xml:space="preserve">芯鼎            </t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>68.90</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+6.2</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>3006</v>
       </c>
@@ -29626,16 +29362,8 @@
           <t xml:space="preserve">正達            </t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>102.00</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+7.9</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>2956</v>
       </c>
@@ -29659,16 +29387,8 @@
           <t xml:space="preserve">永豐金          </t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>2788</v>
       </c>
@@ -29692,16 +29412,8 @@
           <t xml:space="preserve">陽明            </t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>51.60</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>2776</v>
       </c>
@@ -29725,16 +29437,8 @@
           <t xml:space="preserve">台橡            </t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>X0.0</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>2752</v>
       </c>
@@ -29758,16 +29462,8 @@
           <t xml:space="preserve">國喬            </t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>14.00</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>2746</v>
       </c>
@@ -29791,16 +29487,8 @@
           <t xml:space="preserve">長榮            </t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>186.50</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>2724</v>
       </c>
@@ -29824,16 +29512,8 @@
           <t xml:space="preserve">中環            </t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>11.70</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>2611</v>
       </c>
@@ -29857,11 +29537,7 @@
           <t xml:space="preserve">統一            </t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>75.10</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>2563</v>
@@ -29886,16 +29562,8 @@
           <t xml:space="preserve">福懋            </t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>2545</v>
       </c>
@@ -29919,16 +29587,8 @@
           <t xml:space="preserve">嘉晶            </t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>137.50</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>2461</v>
       </c>
@@ -29952,16 +29612,8 @@
           <t xml:space="preserve">超豐            </t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>142.50</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>2456</v>
       </c>
@@ -29985,16 +29637,8 @@
           <t xml:space="preserve">金寶            </t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>38.00</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+3.45</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>2416</v>
       </c>
@@ -30018,16 +29662,8 @@
           <t xml:space="preserve">富鼎            </t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>246.50</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>-13.5</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>2342</v>
       </c>
@@ -30051,16 +29687,8 @@
           <t xml:space="preserve">聯成            </t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>11.80</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>2333</v>
       </c>
@@ -30084,16 +29712,8 @@
           <t xml:space="preserve">聚陽            </t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>217.00</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>2316</v>
       </c>
@@ -30117,16 +29737,8 @@
           <t xml:space="preserve">聯華            </t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>2204</v>
       </c>
@@ -30150,16 +29762,8 @@
           <t xml:space="preserve">矽統            </t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>69.20</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+3.3</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>2199</v>
       </c>
@@ -30183,16 +29787,8 @@
           <t xml:space="preserve">鴻準            </t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>58.00</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+1.4</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>2173</v>
       </c>
@@ -30216,16 +29812,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>2160</v>
       </c>
@@ -30249,16 +29837,8 @@
           <t xml:space="preserve">東陽            </t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>79.50</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>2156</v>
       </c>
@@ -30282,16 +29862,8 @@
           <t xml:space="preserve">大成鋼          </t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>40.55</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>2148</v>
       </c>
@@ -30315,16 +29887,8 @@
           <t xml:space="preserve">東和鋼鐵        </t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>69.80</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>2050</v>
       </c>
@@ -30348,16 +29912,8 @@
           <t xml:space="preserve">彩晶            </t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>19.40</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>1986</v>
       </c>
@@ -30381,16 +29937,8 @@
           <t xml:space="preserve">華夏            </t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>13.30</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>1905</v>
       </c>
@@ -30414,16 +29962,8 @@
           <t xml:space="preserve">建通            </t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>40.45</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+3.65</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>1867</v>
       </c>
@@ -30447,16 +29987,8 @@
           <t xml:space="preserve">國精化          </t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>301.00</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+27.0</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>1782</v>
       </c>
@@ -30480,16 +30012,8 @@
           <t xml:space="preserve">中纖            </t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>9.23</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>1757</v>
       </c>
@@ -30513,16 +30037,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>1700</v>
       </c>
@@ -30546,16 +30062,8 @@
           <t xml:space="preserve">亞聚            </t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>1663</v>
       </c>
@@ -30579,16 +30087,8 @@
           <t xml:space="preserve">智易            </t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>190.50</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+9.5</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>1418</v>
       </c>
@@ -30612,16 +30112,8 @@
           <t xml:space="preserve">國產            </t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>1414</v>
       </c>
@@ -30645,16 +30137,8 @@
           <t xml:space="preserve">潤泰全          </t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>52.60</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>1374</v>
       </c>
@@ -30678,16 +30162,8 @@
           <t xml:space="preserve">大毅            </t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>240.00</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+16.5</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>1308</v>
       </c>
@@ -30711,16 +30187,8 @@
           <t xml:space="preserve">麗正            </t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>50.20</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+4.55</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>1273</v>
       </c>
@@ -30744,16 +30212,8 @@
           <t xml:space="preserve">中砂            </t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>749.00</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>+44.0</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>1221</v>
       </c>
@@ -30777,16 +30237,8 @@
           <t xml:space="preserve">達運            </t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>1177</v>
       </c>
@@ -30810,16 +30262,8 @@
           <t xml:space="preserve">捷敏-KY         </t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>166.00</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>1143</v>
       </c>
@@ -30843,16 +30287,8 @@
           <t xml:space="preserve">技嘉            </t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>339.00</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+8.5</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>1123</v>
       </c>
@@ -30876,16 +30312,8 @@
           <t xml:space="preserve">瑞儀            </t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>90.20</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>1117</v>
       </c>
@@ -30909,16 +30337,8 @@
           <t xml:space="preserve">裕民            </t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>61.40</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>1097</v>
       </c>
@@ -30942,16 +30362,8 @@
           <t xml:space="preserve">順德            </t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>217.50</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+19.5</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>1094</v>
       </c>
@@ -30975,16 +30387,8 @@
           <t xml:space="preserve">上海商銀        </t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>41.55</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>1044</v>
       </c>
@@ -31008,16 +30412,8 @@
           <t xml:space="preserve">永豐餘          </t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>27.50</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>980</v>
       </c>
@@ -31041,16 +30437,8 @@
           <t xml:space="preserve">中興電          </t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>185.00</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>945</v>
       </c>
@@ -31074,16 +30462,8 @@
           <t xml:space="preserve">台中銀          </t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>19.85</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>941</v>
       </c>
@@ -31107,16 +30487,8 @@
           <t xml:space="preserve">華新科          </t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>590.00</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+13.0</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>932</v>
       </c>
@@ -31140,11 +30512,7 @@
           <t xml:space="preserve">工信            </t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>10.40</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
       <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>928</v>
@@ -31169,16 +30537,8 @@
           <t xml:space="preserve">聯鈞            </t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>581.00</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>-31.0</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>916</v>
       </c>
@@ -31202,16 +30562,8 @@
           <t xml:space="preserve">東聯            </t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>13.80</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>887</v>
       </c>
@@ -31235,16 +30587,8 @@
           <t xml:space="preserve">兆豐金          </t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>44.55</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>887</v>
       </c>
@@ -31268,16 +30612,8 @@
           <t xml:space="preserve">統一FANG+       </t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>125.50</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>872</v>
       </c>
@@ -31301,16 +30637,8 @@
           <t xml:space="preserve">貿聯-KY         </t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>2,005.00</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>850</v>
       </c>
@@ -31334,16 +30662,8 @@
           <t xml:space="preserve">中鴻            </t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>17.80</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>835</v>
       </c>
@@ -31367,11 +30687,7 @@
           <t xml:space="preserve">松翰            </t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>62.40</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
       <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>830</v>
@@ -31396,16 +30712,8 @@
           <t xml:space="preserve">界霖            </t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>825</v>
       </c>
@@ -31429,16 +30737,8 @@
           <t xml:space="preserve">奇鋐            </t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>2,530.00</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+105.0</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>814</v>
       </c>
@@ -31462,16 +30762,8 @@
           <t xml:space="preserve">力成            </t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>338.00</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>813</v>
       </c>
@@ -31495,16 +30787,8 @@
           <t xml:space="preserve">力特            </t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+2.25</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>794</v>
       </c>
@@ -31528,16 +30812,8 @@
           <t xml:space="preserve">國際中橡        </t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>10.20</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>784</v>
       </c>
@@ -31561,11 +30837,7 @@
           <t xml:space="preserve">華票            </t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>17.70</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>727</v>
@@ -31590,16 +30862,8 @@
           <t xml:space="preserve">台達化          </t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>715</v>
       </c>
@@ -31623,16 +30887,8 @@
           <t xml:space="preserve">柏承            </t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>38.75</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>685</v>
       </c>
@@ -31656,16 +30912,8 @@
           <t xml:space="preserve">輔信            </t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>18.60</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>684</v>
       </c>
@@ -31689,16 +30937,8 @@
           <t xml:space="preserve">大成            </t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>54.80</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>671</v>
       </c>
@@ -31722,16 +30962,8 @@
           <t xml:space="preserve">建準            </t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>665</v>
       </c>
@@ -31755,11 +30987,7 @@
           <t xml:space="preserve">微星            </t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>133.50</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
       <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>653</v>
@@ -31784,16 +31012,8 @@
           <t xml:space="preserve">亞翔            </t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>818.00</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+27.0</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>640</v>
       </c>
@@ -31894,16 +31114,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>38.08</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-2.12</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-382803</v>
       </c>
@@ -31927,16 +31139,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>107.15</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-2.95</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-162143</v>
       </c>
@@ -31960,16 +31164,8 @@
           <t xml:space="preserve">友達            </t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>30.50</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>+1.45</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-41149</v>
       </c>
@@ -31993,16 +31189,8 @@
           <t xml:space="preserve">台積電          </t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>2,390.00</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-100.0</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-36686</v>
       </c>
@@ -32026,16 +31214,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>30.21</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-26016</v>
       </c>
@@ -32059,16 +31239,8 @@
           <t xml:space="preserve">元大金          </t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>66.10</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-2.2</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-22623</v>
       </c>
@@ -32092,16 +31264,8 @@
           <t xml:space="preserve">群創            </t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>69.40</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>+3.4</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-21698</v>
       </c>
@@ -32125,16 +31289,8 @@
           <t xml:space="preserve">華邦電          </t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>205.00</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-6.5</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-18937</v>
       </c>
@@ -32158,16 +31314,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>53.15</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-17627</v>
       </c>
@@ -32191,16 +31339,8 @@
           <t xml:space="preserve">凱基金          </t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>29.80</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-16587</v>
       </c>
@@ -32224,16 +31364,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>33.66</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-14800</v>
       </c>
@@ -32257,16 +31389,8 @@
           <t xml:space="preserve">玉山金          </t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-13365</v>
       </c>
@@ -32290,16 +31414,8 @@
           <t xml:space="preserve">台新新光金      </t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>31.60</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-12103</v>
       </c>
@@ -32323,16 +31439,8 @@
           <t xml:space="preserve">中信金          </t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>69.90</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-11971</v>
       </c>
@@ -32356,16 +31464,8 @@
           <t xml:space="preserve">鴻海            </t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>256.00</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-11903</v>
       </c>
@@ -32389,16 +31489,8 @@
           <t xml:space="preserve">仁寶            </t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>37.90</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>+1.35</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-10812</v>
       </c>
@@ -32422,16 +31514,8 @@
           <t xml:space="preserve">聯電            </t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>178.00</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-10481</v>
       </c>
@@ -32455,16 +31539,8 @@
           <t xml:space="preserve">台玻            </t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>69.30</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-9367</v>
       </c>
@@ -32488,16 +31564,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>41.12</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-8661</v>
       </c>
@@ -32521,16 +31589,8 @@
           <t>國泰台灣科技龍頭</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>55.35</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-8647</v>
       </c>
@@ -32554,16 +31614,8 @@
           <t xml:space="preserve">群益證          </t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>38.55</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-8593</v>
       </c>
@@ -32587,16 +31639,8 @@
           <t xml:space="preserve">南茂            </t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>103.00</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-8352</v>
       </c>
@@ -32620,16 +31664,8 @@
           <t xml:space="preserve">國泰金          </t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-8042</v>
       </c>
@@ -32653,16 +31689,8 @@
           <t xml:space="preserve">欣興            </t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>931.00</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-43.0</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-7812</v>
       </c>
@@ -32686,16 +31714,8 @@
           <t xml:space="preserve">寶成            </t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-7447</v>
       </c>
@@ -32719,16 +31739,8 @@
           <t xml:space="preserve">緯創            </t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>157.50</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-7330</v>
       </c>
@@ -32752,16 +31764,8 @@
           <t xml:space="preserve">南亞科          </t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>443.50</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-7150</v>
       </c>
@@ -32785,16 +31789,8 @@
           <t xml:space="preserve">台達電          </t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>2,000.00</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>-80.0</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-6849</v>
       </c>
@@ -32818,16 +31814,8 @@
           <t xml:space="preserve">華通            </t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>240.00</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-6480</v>
       </c>
@@ -32851,16 +31839,8 @@
           <t xml:space="preserve">光寶科          </t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>216.50</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-7.0</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-6129</v>
       </c>
@@ -32884,16 +31864,8 @@
           <t xml:space="preserve">日月光投控      </t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>653.00</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-9.0</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-5964</v>
       </c>
@@ -32917,16 +31889,8 @@
           <t xml:space="preserve">康舒            </t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>62.00</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-5157</v>
       </c>
@@ -32950,16 +31914,8 @@
           <t xml:space="preserve">新纖            </t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>27.95</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-5036</v>
       </c>
@@ -32983,16 +31939,8 @@
           <t xml:space="preserve">東元            </t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>71.90</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-4857</v>
       </c>
@@ -33016,16 +31964,8 @@
           <t xml:space="preserve">宏齊            </t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>35.50</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>+1.3</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-4605</v>
       </c>
@@ -33049,16 +31989,8 @@
           <t xml:space="preserve">富邦金          </t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>134.50</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-4486</v>
       </c>
@@ -33082,16 +32014,8 @@
           <t xml:space="preserve">三商壽          </t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>8.51</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-4473</v>
       </c>
@@ -33115,16 +32039,8 @@
           <t xml:space="preserve">材料*-KY        </t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-4383</v>
       </c>
@@ -33148,16 +32064,8 @@
           <t xml:space="preserve">長華*           </t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>57.80</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-4269</v>
       </c>
@@ -33181,16 +32089,8 @@
           <t xml:space="preserve">聯發科          </t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>4,285.00</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-250.0</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-4149</v>
       </c>
@@ -33214,11 +32114,7 @@
           <t xml:space="preserve">臻鼎-KY         </t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>587.00</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
       <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-3841</v>
@@ -33243,11 +32139,7 @@
           <t xml:space="preserve">晶技            </t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>190.50</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
       <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-3613</v>
@@ -33272,16 +32164,8 @@
           <t xml:space="preserve">華新            </t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>38.15</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-3458</v>
       </c>
@@ -33305,16 +32189,8 @@
           <t xml:space="preserve">強茂            </t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>195.00</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-3351</v>
       </c>
@@ -33338,16 +32214,8 @@
           <t xml:space="preserve">亞泥            </t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>36.00</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-3117</v>
       </c>
@@ -33371,16 +32239,8 @@
           <t xml:space="preserve">中租-KY         </t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>113.50</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-2996</v>
       </c>
@@ -33404,16 +32264,8 @@
           <t xml:space="preserve">楠梓電          </t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>220.50</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-2849</v>
       </c>
@@ -33437,16 +32289,8 @@
           <t xml:space="preserve">凱美            </t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>211.50</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-2774</v>
       </c>
@@ -33470,16 +32314,8 @@
           <t xml:space="preserve">鼎元            </t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>93.30</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-2694</v>
       </c>
@@ -33503,11 +32339,7 @@
           <t xml:space="preserve">旺宏            </t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>172.00</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
       <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-2682</v>
@@ -33600,16 +32432,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>10.04</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>+0.22</t>
-        </is>
-      </c>
+      <c r="D164" s="4" t="inlineStr"/>
+      <c r="E164" s="4" t="inlineStr"/>
       <c r="F164" s="4" t="n">
         <v>82225</v>
       </c>
@@ -33629,16 +32453,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>8.60</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>+0.07</t>
-        </is>
-      </c>
+      <c r="D165" s="4" t="inlineStr"/>
+      <c r="E165" s="4" t="inlineStr"/>
       <c r="F165" s="4" t="n">
         <v>10122</v>
       </c>
@@ -33658,16 +32474,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>32.08</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>+0.08</t>
-        </is>
-      </c>
+      <c r="D166" s="4" t="inlineStr"/>
+      <c r="E166" s="4" t="inlineStr"/>
       <c r="F166" s="4" t="n">
         <v>9420</v>
       </c>
@@ -33687,16 +32495,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>12.66</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
+      <c r="D167" s="4" t="inlineStr"/>
+      <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="n">
         <v>6132</v>
       </c>
@@ -33716,16 +32516,8 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>9.64</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>+0.01</t>
-        </is>
-      </c>
+      <c r="D168" s="4" t="inlineStr"/>
+      <c r="E168" s="4" t="inlineStr"/>
       <c r="F168" s="4" t="n">
         <v>4744</v>
       </c>
@@ -33745,16 +32537,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="D169" s="4" t="inlineStr"/>
+      <c r="E169" s="4" t="inlineStr"/>
       <c r="F169" s="4" t="n">
         <v>2160</v>
       </c>
@@ -33774,16 +32558,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="D170" s="4" t="inlineStr"/>
+      <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="n">
         <v>1700</v>
       </c>
@@ -33803,16 +32579,8 @@
           <t xml:space="preserve">統一FANG+       </t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>125.50</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
+      <c r="D171" s="4" t="inlineStr"/>
+      <c r="E171" s="4" t="inlineStr"/>
       <c r="F171" s="4" t="n">
         <v>872</v>
       </c>
@@ -33832,16 +32600,8 @@
           <t xml:space="preserve">元大S&amp;P500      </t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>73.75</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="D172" s="4" t="inlineStr"/>
+      <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="n">
         <v>477</v>
       </c>
@@ -33934,16 +32694,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>38.08</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>-2.12</t>
-        </is>
-      </c>
+      <c r="D178" s="4" t="inlineStr"/>
+      <c r="E178" s="4" t="inlineStr"/>
       <c r="F178" s="4" t="n">
         <v>-382803</v>
       </c>
@@ -33963,16 +32715,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>107.15</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>-2.95</t>
-        </is>
-      </c>
+      <c r="D179" s="4" t="inlineStr"/>
+      <c r="E179" s="4" t="inlineStr"/>
       <c r="F179" s="4" t="n">
         <v>-162143</v>
       </c>
@@ -33992,16 +32736,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>30.21</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
+      <c r="D180" s="4" t="inlineStr"/>
+      <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="n">
         <v>-26016</v>
       </c>
@@ -34021,16 +32757,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>53.15</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="D181" s="4" t="inlineStr"/>
+      <c r="E181" s="4" t="inlineStr"/>
       <c r="F181" s="4" t="n">
         <v>-17627</v>
       </c>
@@ -34050,16 +32778,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>33.66</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
+      <c r="D182" s="4" t="inlineStr"/>
+      <c r="E182" s="4" t="inlineStr"/>
       <c r="F182" s="4" t="n">
         <v>-14800</v>
       </c>
@@ -34079,16 +32799,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>41.12</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
+      <c r="D183" s="4" t="inlineStr"/>
+      <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="n">
         <v>-8661</v>
       </c>
@@ -34108,16 +32820,8 @@
           <t>國泰台灣科技龍頭</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>55.35</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
+      <c r="D184" s="4" t="inlineStr"/>
+      <c r="E184" s="4" t="inlineStr"/>
       <c r="F184" s="4" t="n">
         <v>-8647</v>
       </c>
@@ -34137,16 +32841,8 @@
           <t xml:space="preserve">富邦台50        </t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>247.95</t>
-        </is>
-      </c>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>-6.4</t>
-        </is>
-      </c>
+      <c r="D185" s="4" t="inlineStr"/>
+      <c r="E185" s="4" t="inlineStr"/>
       <c r="F185" s="4" t="n">
         <v>-2340</v>
       </c>
@@ -34166,16 +32862,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="D186" s="4" t="inlineStr">
-        <is>
-          <t>120.45</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
+      <c r="D186" s="4" t="inlineStr"/>
+      <c r="E186" s="4" t="inlineStr"/>
       <c r="F186" s="4" t="n">
         <v>-1344</v>
       </c>
@@ -34195,16 +32883,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="D187" s="4" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="E187" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="D187" s="4" t="inlineStr"/>
+      <c r="E187" s="4" t="inlineStr"/>
       <c r="F187" s="4" t="n">
         <v>-1160</v>
       </c>

--- a/StockInfo/tse_analysis_result.xlsx
+++ b/StockInfo/tse_analysis_result.xlsx
@@ -28683,16 +28683,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>10.56</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>65382</v>
       </c>
@@ -28716,16 +28708,8 @@
           <t xml:space="preserve">群創            </t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>47.35</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>58023</v>
       </c>
@@ -28749,16 +28733,8 @@
           <t xml:space="preserve">聯電            </t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>126.00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>28074</v>
       </c>
@@ -28782,16 +28758,8 @@
           <t xml:space="preserve">台中銀          </t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>20.75</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>24623</v>
       </c>
@@ -28815,16 +28783,8 @@
           <t xml:space="preserve">臺企銀          </t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>18.20</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>21283</v>
       </c>
@@ -28848,16 +28808,8 @@
           <t xml:space="preserve">長榮航          </t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>41.95</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+1.25</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>21029</v>
       </c>
@@ -28881,16 +28833,8 @@
           <t xml:space="preserve">合庫金          </t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>17788</v>
       </c>
@@ -28914,16 +28858,8 @@
           <t xml:space="preserve">中鋼            </t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>17719</v>
       </c>
@@ -28947,16 +28883,8 @@
           <t xml:space="preserve">台泥            </t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>24.40</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>17627</v>
       </c>
@@ -28980,16 +28908,8 @@
           <t xml:space="preserve">永豐金          </t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>39.60</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+1.05</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>17624</v>
       </c>
@@ -29013,16 +28933,8 @@
           <t xml:space="preserve">華航            </t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>16364</v>
       </c>
@@ -29046,16 +28958,8 @@
           <t xml:space="preserve">南亞            </t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>174.00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>16074</v>
       </c>
@@ -29079,16 +28983,8 @@
           <t xml:space="preserve">中纖            </t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>10.25</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>15801</v>
       </c>
@@ -29112,16 +29008,8 @@
           <t xml:space="preserve">三商壽          </t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>9.31</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+0.03</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>14107</v>
       </c>
@@ -29145,16 +29033,8 @@
           <t xml:space="preserve">中華電          </t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>140.50</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>14009</v>
       </c>
@@ -29178,16 +29058,8 @@
           <t xml:space="preserve">玉山金          </t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>36.40</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+0.45</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>11779</v>
       </c>
@@ -29211,16 +29083,8 @@
           <t xml:space="preserve">台新新光金      </t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>11207</v>
       </c>
@@ -29244,16 +29108,8 @@
           <t xml:space="preserve">元大金          </t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>64.70</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>9287</v>
       </c>
@@ -29277,16 +29133,8 @@
           <t xml:space="preserve">華南金          </t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>41.40</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>8669</v>
       </c>
@@ -29310,16 +29158,8 @@
           <t xml:space="preserve">遠東新          </t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>27.45</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>7925</v>
       </c>
@@ -29343,16 +29183,8 @@
           <t xml:space="preserve">凱基金          </t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>30.70</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>7829</v>
       </c>
@@ -29376,11 +29208,7 @@
           <t xml:space="preserve">台灣大          </t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>113.50</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>7216</v>
@@ -29405,16 +29233,8 @@
           <t xml:space="preserve">遠傳            </t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>107.50</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>6917</v>
       </c>
@@ -29438,16 +29258,8 @@
           <t xml:space="preserve">緯創            </t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>177.00</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>6845</v>
       </c>
@@ -29471,16 +29283,8 @@
           <t xml:space="preserve">友訊            </t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>24.30</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+2.2</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>6832</v>
       </c>
@@ -29504,16 +29308,8 @@
           <t xml:space="preserve">上海商銀        </t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>47.00</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>6458</v>
       </c>
@@ -29537,16 +29333,8 @@
           <t xml:space="preserve">彰銀            </t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>24.70</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>5769</v>
       </c>
@@ -29570,16 +29358,8 @@
           <t xml:space="preserve">第一金          </t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>34.80</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>5320</v>
       </c>
@@ -29603,16 +29383,8 @@
           <t xml:space="preserve">國泰金          </t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>98.50</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>5269</v>
       </c>
@@ -29636,16 +29408,8 @@
           <t xml:space="preserve">和桐            </t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>4981</v>
       </c>
@@ -29669,16 +29433,8 @@
           <t xml:space="preserve">王道銀行        </t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>10.30</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>4680</v>
       </c>
@@ -29702,16 +29458,8 @@
           <t xml:space="preserve">富邦金          </t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>130.00</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>4402</v>
       </c>
@@ -29735,16 +29483,8 @@
           <t xml:space="preserve">南茂            </t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>89.90</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>4359</v>
       </c>
@@ -29768,16 +29508,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>12.16</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>3970</v>
       </c>
@@ -29801,16 +29533,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>32.58</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+0.08</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>3346</v>
       </c>
@@ -29834,16 +29558,8 @@
           <t xml:space="preserve">遠東銀          </t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>13.40</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>3074</v>
       </c>
@@ -29867,16 +29583,8 @@
           <t xml:space="preserve">大成鋼          </t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>44.55</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>2727</v>
       </c>
@@ -29900,16 +29608,8 @@
           <t xml:space="preserve">中磊            </t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>90.60</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>2709</v>
       </c>
@@ -29933,16 +29633,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+0.03</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>2622</v>
       </c>
@@ -29966,16 +29658,8 @@
           <t xml:space="preserve">中信中國高股息  </t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+0.04</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>2589</v>
       </c>
@@ -29999,11 +29683,7 @@
           <t xml:space="preserve">中租-KY         </t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>120.00</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>2371</v>
@@ -30028,16 +29708,8 @@
           <t xml:space="preserve">華通            </t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>199.50</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>2267</v>
       </c>
@@ -30061,16 +29733,8 @@
           <t xml:space="preserve">永光            </t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>35.40</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>2152</v>
       </c>
@@ -30094,16 +29758,8 @@
           <t xml:space="preserve">彩晶            </t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>13.25</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>2087</v>
       </c>
@@ -30127,16 +29783,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>8.84</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+0.06</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>2080</v>
       </c>
@@ -30160,16 +29808,8 @@
           <t xml:space="preserve">新唐            </t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>132.50</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>2002</v>
       </c>
@@ -30193,16 +29833,8 @@
           <t xml:space="preserve">亞泥            </t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>33.10</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>1978</v>
       </c>
@@ -30226,16 +29858,8 @@
           <t xml:space="preserve">兆豐金          </t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>49.40</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+0.95</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>1977</v>
       </c>
@@ -30259,16 +29883,8 @@
           <t xml:space="preserve">鴻海            </t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>253.00</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>1905</v>
       </c>
@@ -30292,16 +29908,8 @@
           <t xml:space="preserve">和碩            </t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>87.40</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>1831</v>
       </c>
@@ -30325,16 +29933,8 @@
           <t xml:space="preserve">統一            </t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>77.10</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>1802</v>
       </c>
@@ -30358,16 +29958,8 @@
           <t xml:space="preserve">潤泰新          </t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>26.35</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>1663</v>
       </c>
@@ -30391,16 +29983,8 @@
           <t xml:space="preserve">遠百            </t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>22.30</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>1660</v>
       </c>
@@ -30424,16 +30008,8 @@
           <t xml:space="preserve">宏碁            </t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>30.10</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>1628</v>
       </c>
@@ -30457,16 +30033,8 @@
           <t xml:space="preserve">東和鋼鐵        </t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>73.00</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>1603</v>
       </c>
@@ -30490,16 +30058,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>29.59</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>1404</v>
       </c>
@@ -30523,16 +30083,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>61.20</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>1364</v>
       </c>
@@ -30556,16 +30108,8 @@
           <t xml:space="preserve">台玻            </t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>52.50</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>1310</v>
       </c>
@@ -30589,16 +30133,8 @@
           <t xml:space="preserve">樺漢            </t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>469.00</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>-31.0</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>1263</v>
       </c>
@@ -30622,16 +30158,8 @@
           <t xml:space="preserve">大同            </t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>25.70</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>1224</v>
       </c>
@@ -30655,16 +30183,8 @@
           <t xml:space="preserve">群益證          </t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>35.60</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>1178</v>
       </c>
@@ -30688,16 +30208,8 @@
           <t xml:space="preserve">定穎投控        </t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>114.00</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>1146</v>
       </c>
@@ -30721,11 +30233,7 @@
           <t xml:space="preserve">台灣高鐵        </t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>26.05</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>1110</v>
@@ -30750,16 +30258,8 @@
           <t xml:space="preserve">精誠            </t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>145.50</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+6.0</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>1063</v>
       </c>
@@ -30783,16 +30283,8 @@
           <t xml:space="preserve">昇陽半導體      </t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>311.00</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+10.5</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>1061</v>
       </c>
@@ -30816,16 +30308,8 @@
           <t xml:space="preserve">長榮航太        </t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>194.00</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>1001</v>
       </c>
@@ -30849,16 +30333,8 @@
           <t xml:space="preserve">元大S&amp;P500      </t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>76.20</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>986</v>
       </c>
@@ -30882,16 +30358,8 @@
           <t xml:space="preserve">力山            </t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>32.45</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>928</v>
       </c>
@@ -30915,16 +30383,8 @@
           <t>統一台灣高息動能</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>21.91</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>+0.13</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>920</v>
       </c>
@@ -30948,16 +30408,8 @@
           <t xml:space="preserve">長榮            </t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>203.50</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>877</v>
       </c>
@@ -30981,16 +30433,8 @@
           <t xml:space="preserve">高雄銀          </t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>12.90</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>874</v>
       </c>
@@ -31014,16 +30458,8 @@
           <t xml:space="preserve">三陽工業        </t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>63.10</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>859</v>
       </c>
@@ -31047,16 +30483,8 @@
           <t xml:space="preserve">聯詠            </t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>518.00</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+11.0</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>846</v>
       </c>
@@ -31080,16 +30508,8 @@
           <t xml:space="preserve">日勝生          </t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>829</v>
       </c>
@@ -31113,16 +30533,8 @@
           <t xml:space="preserve">國巨*           </t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>625.00</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>-17.0</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>829</v>
       </c>
@@ -31146,16 +30558,8 @@
           <t xml:space="preserve">國產            </t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>810</v>
       </c>
@@ -31179,16 +30583,8 @@
           <t xml:space="preserve">瑞昱            </t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>762.00</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+18.0</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>795</v>
       </c>
@@ -31212,16 +30608,8 @@
           <t xml:space="preserve">揚博            </t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>210.00</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>785</v>
       </c>
@@ -31245,16 +30633,8 @@
           <t xml:space="preserve">台肥            </t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>46.70</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>749</v>
       </c>
@@ -31278,16 +30658,8 @@
           <t xml:space="preserve">文曄            </t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>203.50</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>747</v>
       </c>
@@ -31311,16 +30683,8 @@
           <t xml:space="preserve">台塑化          </t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>77.90</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>-7.9</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>688</v>
       </c>
@@ -31344,16 +30708,8 @@
           <t xml:space="preserve">瑞軒            </t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>30.05</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>684</v>
       </c>
@@ -31377,16 +30733,8 @@
           <t xml:space="preserve">嘉晶            </t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>94.20</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>658</v>
       </c>
@@ -31410,11 +30758,7 @@
           <t xml:space="preserve">華票            </t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
       <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>651</v>
@@ -31439,16 +30783,8 @@
           <t xml:space="preserve">矽力*-KY        </t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>449.00</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>-18.5</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>650</v>
       </c>
@@ -31472,16 +30808,8 @@
           <t xml:space="preserve">東陽            </t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>73.00</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>591</v>
       </c>
@@ -31505,16 +30833,8 @@
           <t xml:space="preserve">力鵬            </t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>7.34</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>582</v>
       </c>
@@ -31538,16 +30858,8 @@
           <t xml:space="preserve">櫻花建          </t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>41.40</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>571</v>
       </c>
@@ -31571,16 +30883,8 @@
           <t xml:space="preserve">鈺齊-KY         </t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>74.30</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>+2.4</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>564</v>
       </c>
@@ -31604,16 +30908,8 @@
           <t xml:space="preserve">南電            </t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>1,075.00</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>-35.0</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>556</v>
       </c>
@@ -31637,16 +30933,8 @@
           <t xml:space="preserve">南亞科          </t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>436.00</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+35.0</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>526</v>
       </c>
@@ -31670,16 +30958,8 @@
           <t xml:space="preserve">研華            </t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>577.00</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>523</v>
       </c>
@@ -31703,16 +30983,8 @@
           <t xml:space="preserve">雷虎            </t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>186.00</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>516</v>
       </c>
@@ -31736,16 +31008,8 @@
           <t xml:space="preserve">皇昌            </t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>490</v>
       </c>
@@ -31769,16 +31033,8 @@
           <t xml:space="preserve">裕融            </t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>82.40</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>484</v>
       </c>
@@ -31802,16 +31058,8 @@
           <t xml:space="preserve">兆赫            </t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>40.60</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>481</v>
       </c>
@@ -31835,16 +31083,8 @@
           <t xml:space="preserve">臻鼎-KY         </t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>470.50</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>-11.5</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>472</v>
       </c>
@@ -31868,16 +31108,8 @@
           <t xml:space="preserve">北極星藥業-KY   </t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>471</v>
       </c>
@@ -31901,16 +31133,8 @@
           <t xml:space="preserve">力積電          </t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>61.90</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>468</v>
       </c>
@@ -31934,16 +31158,8 @@
           <t xml:space="preserve">基泰            </t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>10.05</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>465</v>
       </c>
@@ -32044,16 +31260,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>101.45</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-37211</v>
       </c>
@@ -32077,16 +31285,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>33.54</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>+0.04</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-29070</v>
       </c>
@@ -32110,16 +31310,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-22411</v>
       </c>
@@ -32143,16 +31335,8 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>9.82</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>+0.03</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-14800</v>
       </c>
@@ -32176,16 +31360,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>32.55</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-12837</v>
       </c>
@@ -32209,16 +31385,8 @@
           <t xml:space="preserve">至上            </t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>84.30</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-11684</v>
       </c>
@@ -32242,16 +31410,8 @@
           <t xml:space="preserve">漢翔            </t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>61.80</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-3.6</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-11420</v>
       </c>
@@ -32275,16 +31435,8 @@
           <t xml:space="preserve">華邦電          </t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>160.00</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-9853</v>
       </c>
@@ -32308,16 +31460,8 @@
           <t xml:space="preserve">中石化          </t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>8.04</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-9841</v>
       </c>
@@ -32341,16 +31485,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>28.54</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-9825</v>
       </c>
@@ -32374,16 +31510,8 @@
           <t xml:space="preserve">友達            </t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>23.90</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-9095</v>
       </c>
@@ -32407,16 +31535,8 @@
           <t xml:space="preserve">國喬            </t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>12.25</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-7693</v>
       </c>
@@ -32440,16 +31560,8 @@
           <t xml:space="preserve">台塑            </t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>61.70</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-5354</v>
       </c>
@@ -32473,16 +31585,8 @@
           <t xml:space="preserve">中工            </t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-4492</v>
       </c>
@@ -32506,16 +31610,8 @@
           <t xml:space="preserve">台虹            </t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>216.00</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-24.0</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-3865</v>
       </c>
@@ -32539,16 +31635,8 @@
           <t xml:space="preserve">國際中橡        </t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-3833</v>
       </c>
@@ -32572,16 +31660,8 @@
           <t xml:space="preserve">中信金          </t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>63.00</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-3771</v>
       </c>
@@ -32605,16 +31685,8 @@
           <t xml:space="preserve">華新            </t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-3549</v>
       </c>
@@ -32638,16 +31710,8 @@
           <t xml:space="preserve">台化            </t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-3439</v>
       </c>
@@ -32671,16 +31735,8 @@
           <t xml:space="preserve">台聚            </t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>12.25</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-3412</v>
       </c>
@@ -32704,16 +31760,8 @@
           <t xml:space="preserve">東聯            </t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>14.65</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-3407</v>
       </c>
@@ -32737,16 +31785,8 @@
           <t xml:space="preserve">旺宏            </t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>125.50</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-3093</v>
       </c>
@@ -32770,16 +31810,8 @@
           <t xml:space="preserve">亞翔            </t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>762.00</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-78.0</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-2877</v>
       </c>
@@ -32803,16 +31835,8 @@
           <t xml:space="preserve">仁寶            </t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>37.15</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-2714</v>
       </c>
@@ -32836,16 +31860,8 @@
           <t xml:space="preserve">聯成            </t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>11.30</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-2402</v>
       </c>
@@ -32869,16 +31885,8 @@
           <t xml:space="preserve">國碩            </t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>33.25</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-2300</v>
       </c>
@@ -32902,16 +31910,8 @@
           <t xml:space="preserve">光寶科          </t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>212.00</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-2272</v>
       </c>
@@ -32935,16 +31935,8 @@
           <t xml:space="preserve">中環            </t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>10.30</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-2196</v>
       </c>
@@ -32968,16 +31960,8 @@
           <t xml:space="preserve">華夏            </t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>11.85</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-2052</v>
       </c>
@@ -33001,16 +31985,8 @@
           <t xml:space="preserve">威健            </t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>48.95</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-2042</v>
       </c>
@@ -33034,16 +32010,8 @@
           <t xml:space="preserve">達運            </t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>12.60</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-2016</v>
       </c>
@@ -33067,16 +32035,8 @@
           <t xml:space="preserve">萬海            </t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>84.00</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-1940</v>
       </c>
@@ -33100,16 +32060,8 @@
           <t>國泰台灣科技龍頭</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>51.05</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-1891</v>
       </c>
@@ -33133,16 +32085,8 @@
           <t xml:space="preserve">興富發          </t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>43.50</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-1883</v>
       </c>
@@ -33166,16 +32110,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>38.97</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-1791</v>
       </c>
@@ -33199,16 +32135,8 @@
           <t xml:space="preserve">可寧衛*         </t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>25.70</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-1788</v>
       </c>
@@ -33232,16 +32160,8 @@
           <t xml:space="preserve">陽明            </t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>51.10</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-1784</v>
       </c>
@@ -33265,16 +32185,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>118.80</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-1720</v>
       </c>
@@ -33298,16 +32210,8 @@
           <t xml:space="preserve">柏承            </t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>-3.7</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-1637</v>
       </c>
@@ -33331,16 +32235,8 @@
           <t xml:space="preserve">台達化          </t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>13.85</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-1557</v>
       </c>
@@ -33364,16 +32260,8 @@
           <t xml:space="preserve">亞聚            </t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>13.30</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-1478</v>
       </c>
@@ -33397,16 +32285,8 @@
           <t xml:space="preserve">創見            </t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>272.00</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>+8.0</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-1465</v>
       </c>
@@ -33430,16 +32310,8 @@
           <t xml:space="preserve">英業達          </t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>63.80</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-1441</v>
       </c>
@@ -33463,16 +32335,8 @@
           <t xml:space="preserve">京元電子        </t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>276.00</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-1373</v>
       </c>
@@ -33496,16 +32360,8 @@
           <t xml:space="preserve">福懋            </t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-1335</v>
       </c>
@@ -33529,16 +32385,8 @@
           <t xml:space="preserve">富邦台50        </t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>232.75</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-1295</v>
       </c>
@@ -33562,16 +32410,8 @@
           <t xml:space="preserve">材料*-KY        </t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>49.70</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-1257</v>
       </c>
@@ -33595,16 +32435,8 @@
           <t xml:space="preserve">希華            </t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>73.10</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-1244</v>
       </c>
@@ -33628,16 +32460,8 @@
           <t xml:space="preserve">泰山            </t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>15.80</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-1146</v>
       </c>
@@ -33661,16 +32485,8 @@
           <t xml:space="preserve">國建            </t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-1114</v>
       </c>
@@ -33762,16 +32578,8 @@
           <t xml:space="preserve">元大台灣50反1   </t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>10.56</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
+      <c r="D164" s="4" t="inlineStr"/>
+      <c r="E164" s="4" t="inlineStr"/>
       <c r="F164" s="4" t="n">
         <v>65382</v>
       </c>
@@ -33791,16 +32599,8 @@
           <t>元大台灣價值高息</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>12.16</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
+      <c r="D165" s="4" t="inlineStr"/>
+      <c r="E165" s="4" t="inlineStr"/>
       <c r="F165" s="4" t="n">
         <v>3970</v>
       </c>
@@ -33820,16 +32620,8 @@
           <t>大華優利高填息30</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>32.58</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>+0.08</t>
-        </is>
-      </c>
+      <c r="D166" s="4" t="inlineStr"/>
+      <c r="E166" s="4" t="inlineStr"/>
       <c r="F166" s="4" t="n">
         <v>3346</v>
       </c>
@@ -33849,16 +32641,8 @@
           <t>富邦特選高股息30</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>+0.03</t>
-        </is>
-      </c>
+      <c r="D167" s="4" t="inlineStr"/>
+      <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="n">
         <v>2622</v>
       </c>
@@ -33878,16 +32662,8 @@
           <t xml:space="preserve">中信中國高股息  </t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>+0.04</t>
-        </is>
-      </c>
+      <c r="D168" s="4" t="inlineStr"/>
+      <c r="E168" s="4" t="inlineStr"/>
       <c r="F168" s="4" t="n">
         <v>2589</v>
       </c>
@@ -33907,16 +32683,8 @@
           <t xml:space="preserve">復華富時不動產  </t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>8.84</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>+0.06</t>
-        </is>
-      </c>
+      <c r="D169" s="4" t="inlineStr"/>
+      <c r="E169" s="4" t="inlineStr"/>
       <c r="F169" s="4" t="n">
         <v>2080</v>
       </c>
@@ -33936,16 +32704,8 @@
           <t>群益台灣精選高息</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>29.59</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="D170" s="4" t="inlineStr"/>
+      <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="n">
         <v>1404</v>
       </c>
@@ -33965,16 +32725,8 @@
           <t>元大台灣高息低波</t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>61.20</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="D171" s="4" t="inlineStr"/>
+      <c r="E171" s="4" t="inlineStr"/>
       <c r="F171" s="4" t="n">
         <v>1364</v>
       </c>
@@ -33994,16 +32746,8 @@
           <t xml:space="preserve">元大S&amp;P500      </t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>76.20</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="D172" s="4" t="inlineStr"/>
+      <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="n">
         <v>986</v>
       </c>
@@ -34023,16 +32767,8 @@
           <t>統一台灣高息動能</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>21.91</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>+0.13</t>
-        </is>
-      </c>
+      <c r="D173" s="4" t="inlineStr"/>
+      <c r="E173" s="4" t="inlineStr"/>
       <c r="F173" s="4" t="n">
         <v>920</v>
       </c>
@@ -34125,16 +32861,8 @@
           <t xml:space="preserve">元大台灣50      </t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>101.45</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="D179" s="4" t="inlineStr"/>
+      <c r="E179" s="4" t="inlineStr"/>
       <c r="F179" s="4" t="n">
         <v>-37211</v>
       </c>
@@ -34154,16 +32882,8 @@
           <t xml:space="preserve">元大台灣50正2   </t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>33.54</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>+0.04</t>
-        </is>
-      </c>
+      <c r="D180" s="4" t="inlineStr"/>
+      <c r="E180" s="4" t="inlineStr"/>
       <c r="F180" s="4" t="n">
         <v>-29070</v>
       </c>
@@ -34183,16 +32903,8 @@
           <t xml:space="preserve">元大高股息      </t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="D181" s="4" t="inlineStr"/>
+      <c r="E181" s="4" t="inlineStr"/>
       <c r="F181" s="4" t="n">
         <v>-22411</v>
       </c>
@@ -34212,16 +32924,8 @@
           <t>群益優選非投等債</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>9.82</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>+0.03</t>
-        </is>
-      </c>
+      <c r="D182" s="4" t="inlineStr"/>
+      <c r="E182" s="4" t="inlineStr"/>
       <c r="F182" s="4" t="n">
         <v>-14800</v>
       </c>
@@ -34241,16 +32945,8 @@
           <t xml:space="preserve">國泰永續高股息  </t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>32.55</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
+      <c r="D183" s="4" t="inlineStr"/>
+      <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="n">
         <v>-12837</v>
       </c>
@@ -34270,16 +32966,8 @@
           <t>復華台灣科技優息</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>28.54</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
+      <c r="D184" s="4" t="inlineStr"/>
+      <c r="E184" s="4" t="inlineStr"/>
       <c r="F184" s="4" t="n">
         <v>-9825</v>
       </c>
@@ -34299,16 +32987,8 @@
           <t>國泰台灣科技龍頭</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>51.05</t>
-        </is>
-      </c>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="D185" s="4" t="inlineStr"/>
+      <c r="E185" s="4" t="inlineStr"/>
       <c r="F185" s="4" t="n">
         <v>-1891</v>
       </c>
@@ -34328,16 +33008,8 @@
           <t xml:space="preserve">國泰台灣領袖50  </t>
         </is>
       </c>
-      <c r="D186" s="4" t="inlineStr">
-        <is>
-          <t>38.97</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
+      <c r="D186" s="4" t="inlineStr"/>
+      <c r="E186" s="4" t="inlineStr"/>
       <c r="F186" s="4" t="n">
         <v>-1791</v>
       </c>
@@ -34357,16 +33029,8 @@
           <t xml:space="preserve">富邦NASDAQ      </t>
         </is>
       </c>
-      <c r="D187" s="4" t="inlineStr">
-        <is>
-          <t>118.80</t>
-        </is>
-      </c>
-      <c r="E187" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="D187" s="4" t="inlineStr"/>
+      <c r="E187" s="4" t="inlineStr"/>
       <c r="F187" s="4" t="n">
         <v>-1720</v>
       </c>
@@ -34386,16 +33050,8 @@
           <t xml:space="preserve">富邦台50        </t>
         </is>
       </c>
-      <c r="D188" s="4" t="inlineStr">
-        <is>
-          <t>232.75</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="D188" s="4" t="inlineStr"/>
+      <c r="E188" s="4" t="inlineStr"/>
       <c r="F188" s="4" t="n">
         <v>-1295</v>
       </c>
